--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ3"/>
+  <dimension ref="A1:GR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -724,6 +724,7 @@
     <col width="10" customWidth="1" min="197" max="197"/>
     <col width="10" customWidth="1" min="198" max="198"/>
     <col width="10" customWidth="1" min="199" max="199"/>
+    <col width="10" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1328,6 +1329,9 @@
       <c r="GQ1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="GR1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1931,6 +1935,9 @@
       <c r="GQ2" t="n">
         <v>22</v>
       </c>
+      <c r="GR2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2533,6 +2540,9 @@
       </c>
       <c r="GQ3" t="n">
         <v>0</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>-7</v>
       </c>
     </row>
   </sheetData>
@@ -2546,7 +2556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IE3"/>
+  <dimension ref="A1:IF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2788,6 +2798,7 @@
     <col width="12" customWidth="1" min="237" max="237"/>
     <col width="12" customWidth="1" min="238" max="238"/>
     <col width="12" customWidth="1" min="239" max="239"/>
+    <col width="12" customWidth="1" min="240" max="240"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3986,6 +3997,11 @@
           <t>20260904</t>
         </is>
       </c>
+      <c r="IF1" s="1" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4649,6 +4665,9 @@
       <c r="IE2" t="n">
         <v>100</v>
       </c>
+      <c r="IF2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5371,6 +5390,9 @@
       </c>
       <c r="IE3" t="n">
         <v>101</v>
+      </c>
+      <c r="IF3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -5384,7 +5406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HL3"/>
+  <dimension ref="A1:HM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5607,6 +5629,7 @@
     <col width="12" customWidth="1" min="218" max="218"/>
     <col width="12" customWidth="1" min="219" max="219"/>
     <col width="12" customWidth="1" min="220" max="220"/>
+    <col width="12" customWidth="1" min="221" max="221"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6710,6 +6733,11 @@
           <t>20260904</t>
         </is>
       </c>
+      <c r="HM1" s="1" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7259,6 +7287,9 @@
       <c r="HL2" t="n">
         <v>-45.94</v>
       </c>
+      <c r="HM2" t="n">
+        <v>-45.93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7924,6 +7955,9 @@
       </c>
       <c r="HL3" t="n">
         <v>-38.14</v>
+      </c>
+      <c r="HM3" t="n">
+        <v>-38.71</v>
       </c>
     </row>
   </sheetData>
@@ -7937,7 +7971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ3"/>
+  <dimension ref="A1:GR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8139,6 +8173,7 @@
     <col width="12" customWidth="1" min="197" max="197"/>
     <col width="12" customWidth="1" min="198" max="198"/>
     <col width="12" customWidth="1" min="199" max="199"/>
+    <col width="12" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9137,6 +9172,11 @@
           <t>20260904</t>
         </is>
       </c>
+      <c r="GR1" s="1" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9560,6 +9600,9 @@
       <c r="GQ2" t="n">
         <v>2</v>
       </c>
+      <c r="GR2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10162,6 +10205,9 @@
       </c>
       <c r="GQ3" t="n">
         <v>8</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -10175,7 +10221,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HU3"/>
+  <dimension ref="A1:HV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10407,6 +10453,7 @@
     <col width="10" customWidth="1" min="227" max="227"/>
     <col width="10" customWidth="1" min="228" max="228"/>
     <col width="10" customWidth="1" min="229" max="229"/>
+    <col width="10" customWidth="1" min="230" max="230"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11101,6 +11148,9 @@
       <c r="HU1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="HV1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11794,6 +11844,9 @@
       <c r="HU2" t="n">
         <v>29</v>
       </c>
+      <c r="HV2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12486,6 +12539,9 @@
       </c>
       <c r="HU3" t="n">
         <v>23</v>
+      </c>
+      <c r="HV3" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -12499,7 +12555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI3"/>
+  <dimension ref="A1:EJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12641,6 +12697,7 @@
     <col width="10" customWidth="1" min="137" max="137"/>
     <col width="10" customWidth="1" min="138" max="138"/>
     <col width="10" customWidth="1" min="139" max="139"/>
+    <col width="10" customWidth="1" min="140" max="140"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13065,6 +13122,9 @@
       <c r="EI1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="EJ1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13488,6 +13548,9 @@
       <c r="EI2" t="n">
         <v>86</v>
       </c>
+      <c r="EJ2" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13910,6 +13973,9 @@
       </c>
       <c r="EI3" t="n">
         <v>70</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -13923,7 +13989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EI3"/>
+  <dimension ref="A1:EJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14065,6 +14131,7 @@
     <col width="10" customWidth="1" min="137" max="137"/>
     <col width="10" customWidth="1" min="138" max="138"/>
     <col width="10" customWidth="1" min="139" max="139"/>
+    <col width="10" customWidth="1" min="140" max="140"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14489,6 +14556,9 @@
       <c r="EI1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="EJ1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14912,6 +14982,9 @@
       <c r="EI2" t="n">
         <v>34</v>
       </c>
+      <c r="EJ2" t="n">
+        <v>31</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15334,6 +15407,9 @@
       </c>
       <c r="EI3" t="n">
         <v>21</v>
+      </c>
+      <c r="EJ3" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -15347,7 +15423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ3"/>
+  <dimension ref="A1:GR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15549,6 +15625,7 @@
     <col width="12" customWidth="1" min="197" max="197"/>
     <col width="12" customWidth="1" min="198" max="198"/>
     <col width="12" customWidth="1" min="199" max="199"/>
+    <col width="12" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16547,6 +16624,11 @@
           <t>20260904</t>
         </is>
       </c>
+      <c r="GR1" s="1" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16970,6 +17052,9 @@
       <c r="GQ2" t="n">
         <v>101</v>
       </c>
+      <c r="GR2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17572,6 +17657,9 @@
       </c>
       <c r="GQ3" t="n">
         <v>100</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -17585,7 +17673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IE3"/>
+  <dimension ref="A1:IF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17827,6 +17915,7 @@
     <col width="12" customWidth="1" min="237" max="237"/>
     <col width="12" customWidth="1" min="238" max="238"/>
     <col width="12" customWidth="1" min="239" max="239"/>
+    <col width="12" customWidth="1" min="240" max="240"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19025,6 +19114,11 @@
           <t>20260904</t>
         </is>
       </c>
+      <c r="IF1" s="1" t="inlineStr">
+        <is>
+          <t>20260908</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19688,6 +19782,9 @@
       <c r="IE2" t="n">
         <v>7.95</v>
       </c>
+      <c r="IF2" t="n">
+        <v>7.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20410,6 +20507,9 @@
       </c>
       <c r="IE3" t="n">
         <v>2.59</v>
+      </c>
+      <c r="IF3" t="n">
+        <v>2.49</v>
       </c>
     </row>
   </sheetData>
@@ -20423,7 +20523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IX3"/>
+  <dimension ref="A1:IY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20684,6 +20784,7 @@
     <col width="12" customWidth="1" min="256" max="256"/>
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21465,6 +21566,9 @@
       <c r="IX1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IY1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22242,6 +22346,9 @@
       <c r="IX2" t="n">
         <v>720.91</v>
       </c>
+      <c r="IY2" t="n">
+        <v>718.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23021,6 +23128,9 @@
       </c>
       <c r="IX3" t="n">
         <v>72.38</v>
+      </c>
+      <c r="IY3" t="n">
+        <v>72.13</v>
       </c>
     </row>
   </sheetData>
@@ -23034,7 +23144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IX3"/>
+  <dimension ref="A1:IY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23295,6 +23405,7 @@
     <col width="12" customWidth="1" min="256" max="256"/>
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24076,6 +24187,9 @@
       <c r="IX1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IY1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24853,6 +24967,9 @@
       <c r="IX2" t="n">
         <v>722.08</v>
       </c>
+      <c r="IY2" t="n">
+        <v>723.76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25632,6 +25749,9 @@
       </c>
       <c r="IX3" t="n">
         <v>73.28</v>
+      </c>
+      <c r="IY3" t="n">
+        <v>73.8</v>
       </c>
     </row>
   </sheetData>
@@ -25645,7 +25765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IX3"/>
+  <dimension ref="A1:IY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -25906,6 +26026,7 @@
     <col width="12" customWidth="1" min="256" max="256"/>
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26687,6 +26808,9 @@
       <c r="IX1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IY1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27464,6 +27588,9 @@
       <c r="IX2" t="n">
         <v>711.2464</v>
       </c>
+      <c r="IY2" t="n">
+        <v>716.9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28243,6 +28370,9 @@
       </c>
       <c r="IX3" t="n">
         <v>72.03</v>
+      </c>
+      <c r="IY3" t="n">
+        <v>71.72</v>
       </c>
     </row>
   </sheetData>
@@ -28256,7 +28386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IX3"/>
+  <dimension ref="A1:IY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28517,6 +28647,7 @@
     <col width="12" customWidth="1" min="256" max="256"/>
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29298,6 +29429,9 @@
       <c r="IX1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IY1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30075,6 +30209,9 @@
       <c r="IX2" t="n">
         <v>720.7</v>
       </c>
+      <c r="IY2" t="n">
+        <v>718.62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30854,6 +30991,9 @@
       </c>
       <c r="IX3" t="n">
         <v>72.88</v>
+      </c>
+      <c r="IY3" t="n">
+        <v>72.23999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -30867,7 +31007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IX3"/>
+  <dimension ref="A1:IY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31128,6 +31268,7 @@
     <col width="12" customWidth="1" min="256" max="256"/>
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
+    <col width="12" customWidth="1" min="259" max="259"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31909,6 +32050,9 @@
       <c r="IX1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IY1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32686,6 +32830,9 @@
       <c r="IX2" t="n">
         <v>214463</v>
       </c>
+      <c r="IY2" t="n">
+        <v>311333</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33465,6 +33612,9 @@
       </c>
       <c r="IX3" t="n">
         <v>1053810</v>
+      </c>
+      <c r="IY3" t="n">
+        <v>1382426</v>
       </c>
     </row>
   </sheetData>
@@ -33478,7 +33628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IE3"/>
+  <dimension ref="A1:IF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33720,6 +33870,7 @@
     <col width="10" customWidth="1" min="237" max="237"/>
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
+    <col width="10" customWidth="1" min="240" max="240"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34444,6 +34595,9 @@
       <c r="IE1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IF1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35167,6 +35321,9 @@
       <c r="IE2" t="n">
         <v>49</v>
       </c>
+      <c r="IF2" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35889,6 +36046,9 @@
       </c>
       <c r="IE3" t="n">
         <v>43</v>
+      </c>
+      <c r="IF3" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -35902,7 +36062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GQ3"/>
+  <dimension ref="A1:GR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36104,6 +36264,7 @@
     <col width="10" customWidth="1" min="197" max="197"/>
     <col width="10" customWidth="1" min="198" max="198"/>
     <col width="10" customWidth="1" min="199" max="199"/>
+    <col width="10" customWidth="1" min="200" max="200"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36708,6 +36869,9 @@
       <c r="GQ1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="GR1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37311,6 +37475,9 @@
       <c r="GQ2" t="n">
         <v>70</v>
       </c>
+      <c r="GR2" t="n">
+        <v>67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37913,6 +38080,9 @@
       </c>
       <c r="GQ3" t="n">
         <v>54</v>
+      </c>
+      <c r="GR3" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -37926,7 +38096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IE3"/>
+  <dimension ref="A1:IF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38168,6 +38338,7 @@
     <col width="10" customWidth="1" min="237" max="237"/>
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
+    <col width="10" customWidth="1" min="240" max="240"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38892,6 +39063,9 @@
       <c r="IE1" s="1" t="n">
         <v>20260904</v>
       </c>
+      <c r="IF1" s="1" t="n">
+        <v>20260908</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39615,6 +39789,9 @@
       <c r="IE2" t="n">
         <v>18</v>
       </c>
+      <c r="IF2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40337,6 +40514,9 @@
       </c>
       <c r="IE3" t="n">
         <v>8</v>
+      </c>
+      <c r="IF3" t="n">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR3"/>
+  <dimension ref="A1:GS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -725,6 +725,7 @@
     <col width="10" customWidth="1" min="198" max="198"/>
     <col width="10" customWidth="1" min="199" max="199"/>
     <col width="10" customWidth="1" min="200" max="200"/>
+    <col width="10" customWidth="1" min="201" max="201"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1332,6 +1333,9 @@
       <c r="GR1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="GS1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1938,6 +1942,9 @@
       <c r="GR2" t="n">
         <v>14</v>
       </c>
+      <c r="GS2" t="n">
+        <v>-1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2543,6 +2550,9 @@
       </c>
       <c r="GR3" t="n">
         <v>-7</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>-20</v>
       </c>
     </row>
   </sheetData>
@@ -2556,7 +2566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IF3"/>
+  <dimension ref="A1:IG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2799,6 +2809,7 @@
     <col width="12" customWidth="1" min="238" max="238"/>
     <col width="12" customWidth="1" min="239" max="239"/>
     <col width="12" customWidth="1" min="240" max="240"/>
+    <col width="12" customWidth="1" min="241" max="241"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4002,6 +4013,11 @@
           <t>20260908</t>
         </is>
       </c>
+      <c r="IG1" s="1" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4668,6 +4684,9 @@
       <c r="IF2" t="n">
         <v>100</v>
       </c>
+      <c r="IG2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5393,6 +5412,9 @@
       </c>
       <c r="IF3" t="n">
         <v>100</v>
+      </c>
+      <c r="IG3" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5406,7 +5428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HM3"/>
+  <dimension ref="A1:HN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5630,6 +5652,7 @@
     <col width="12" customWidth="1" min="219" max="219"/>
     <col width="12" customWidth="1" min="220" max="220"/>
     <col width="12" customWidth="1" min="221" max="221"/>
+    <col width="12" customWidth="1" min="222" max="222"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6738,6 +6761,11 @@
           <t>20260908</t>
         </is>
       </c>
+      <c r="HN1" s="1" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7290,6 +7318,9 @@
       <c r="HM2" t="n">
         <v>-45.93</v>
       </c>
+      <c r="HN2" t="n">
+        <v>-44.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7958,6 +7989,9 @@
       </c>
       <c r="HM3" t="n">
         <v>-38.71</v>
+      </c>
+      <c r="HN3" t="n">
+        <v>-36.92</v>
       </c>
     </row>
   </sheetData>
@@ -7971,7 +8005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR3"/>
+  <dimension ref="A1:GS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8174,6 +8208,7 @@
     <col width="12" customWidth="1" min="198" max="198"/>
     <col width="12" customWidth="1" min="199" max="199"/>
     <col width="12" customWidth="1" min="200" max="200"/>
+    <col width="12" customWidth="1" min="201" max="201"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9177,6 +9212,11 @@
           <t>20260908</t>
         </is>
       </c>
+      <c r="GS1" s="1" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9603,6 +9643,9 @@
       <c r="GR2" t="n">
         <v>4</v>
       </c>
+      <c r="GS2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10208,6 +10251,9 @@
       </c>
       <c r="GR3" t="n">
         <v>10</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -10221,7 +10267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HV3"/>
+  <dimension ref="A1:HW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10454,6 +10500,7 @@
     <col width="10" customWidth="1" min="228" max="228"/>
     <col width="10" customWidth="1" min="229" max="229"/>
     <col width="10" customWidth="1" min="230" max="230"/>
+    <col width="10" customWidth="1" min="231" max="231"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11151,6 +11198,9 @@
       <c r="HV1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="HW1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11847,6 +11897,9 @@
       <c r="HV2" t="n">
         <v>21</v>
       </c>
+      <c r="HW2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12542,6 +12595,9 @@
       </c>
       <c r="HV3" t="n">
         <v>14</v>
+      </c>
+      <c r="HW3" t="n">
+        <v>-6</v>
       </c>
     </row>
   </sheetData>
@@ -12555,7 +12611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ3"/>
+  <dimension ref="A1:EK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12698,6 +12754,7 @@
     <col width="10" customWidth="1" min="138" max="138"/>
     <col width="10" customWidth="1" min="139" max="139"/>
     <col width="10" customWidth="1" min="140" max="140"/>
+    <col width="10" customWidth="1" min="141" max="141"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13125,6 +13182,9 @@
       <c r="EJ1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="EK1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13551,6 +13611,9 @@
       <c r="EJ2" t="n">
         <v>85</v>
       </c>
+      <c r="EK2" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13976,6 +14039,9 @@
       </c>
       <c r="EJ3" t="n">
         <v>69</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -13989,7 +14055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EJ3"/>
+  <dimension ref="A1:EK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14132,6 +14198,7 @@
     <col width="10" customWidth="1" min="138" max="138"/>
     <col width="10" customWidth="1" min="139" max="139"/>
     <col width="10" customWidth="1" min="140" max="140"/>
+    <col width="10" customWidth="1" min="141" max="141"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14559,6 +14626,9 @@
       <c r="EJ1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="EK1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14985,6 +15055,9 @@
       <c r="EJ2" t="n">
         <v>31</v>
       </c>
+      <c r="EK2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15410,6 +15483,9 @@
       </c>
       <c r="EJ3" t="n">
         <v>18</v>
+      </c>
+      <c r="EK3" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -15423,7 +15499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR3"/>
+  <dimension ref="A1:GS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15626,6 +15702,7 @@
     <col width="12" customWidth="1" min="198" max="198"/>
     <col width="12" customWidth="1" min="199" max="199"/>
     <col width="12" customWidth="1" min="200" max="200"/>
+    <col width="12" customWidth="1" min="201" max="201"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16629,6 +16706,11 @@
           <t>20260908</t>
         </is>
       </c>
+      <c r="GS1" s="1" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17055,6 +17137,9 @@
       <c r="GR2" t="n">
         <v>101</v>
       </c>
+      <c r="GS2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17660,6 +17745,9 @@
       </c>
       <c r="GR3" t="n">
         <v>99</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -17673,7 +17761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IF3"/>
+  <dimension ref="A1:IG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -17916,6 +18004,7 @@
     <col width="12" customWidth="1" min="238" max="238"/>
     <col width="12" customWidth="1" min="239" max="239"/>
     <col width="12" customWidth="1" min="240" max="240"/>
+    <col width="12" customWidth="1" min="241" max="241"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19119,6 +19208,11 @@
           <t>20260908</t>
         </is>
       </c>
+      <c r="IG1" s="1" t="inlineStr">
+        <is>
+          <t>20260909</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19785,6 +19879,9 @@
       <c r="IF2" t="n">
         <v>7.71</v>
       </c>
+      <c r="IG2" t="n">
+        <v>7.7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20509,6 +20606,9 @@
         <v>2.59</v>
       </c>
       <c r="IF3" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="IG3" t="n">
         <v>2.49</v>
       </c>
     </row>
@@ -20523,7 +20623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IY3"/>
+  <dimension ref="A1:IZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20785,6 +20885,7 @@
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21569,6 +21670,9 @@
       <c r="IY1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IZ1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22349,6 +22453,9 @@
       <c r="IY2" t="n">
         <v>718.21</v>
       </c>
+      <c r="IZ2" t="n">
+        <v>719.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23131,6 +23238,9 @@
       </c>
       <c r="IY3" t="n">
         <v>72.13</v>
+      </c>
+      <c r="IZ3" t="n">
+        <v>72.51000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -23144,7 +23254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IY3"/>
+  <dimension ref="A1:IZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23406,6 +23516,7 @@
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24190,6 +24301,9 @@
       <c r="IY1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IZ1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24970,6 +25084,9 @@
       <c r="IY2" t="n">
         <v>723.76</v>
       </c>
+      <c r="IZ2" t="n">
+        <v>720.78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25752,6 +25869,9 @@
       </c>
       <c r="IY3" t="n">
         <v>73.8</v>
+      </c>
+      <c r="IZ3" t="n">
+        <v>72.83</v>
       </c>
     </row>
   </sheetData>
@@ -25765,7 +25885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IY3"/>
+  <dimension ref="A1:IZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26027,6 +26147,7 @@
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26811,6 +26932,9 @@
       <c r="IY1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IZ1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27591,6 +27715,9 @@
       <c r="IY2" t="n">
         <v>716.9</v>
       </c>
+      <c r="IZ2" t="n">
+        <v>713.45</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28373,6 +28500,9 @@
       </c>
       <c r="IY3" t="n">
         <v>71.72</v>
+      </c>
+      <c r="IZ3" t="n">
+        <v>70.6699</v>
       </c>
     </row>
   </sheetData>
@@ -28386,7 +28516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IY3"/>
+  <dimension ref="A1:IZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28648,6 +28778,7 @@
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29432,6 +29563,9 @@
       <c r="IY1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IZ1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30212,6 +30346,9 @@
       <c r="IY2" t="n">
         <v>718.62</v>
       </c>
+      <c r="IZ2" t="n">
+        <v>714.0739</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -30994,6 +31131,9 @@
       </c>
       <c r="IY3" t="n">
         <v>72.23999999999999</v>
+      </c>
+      <c r="IZ3" t="n">
+        <v>70.84</v>
       </c>
     </row>
   </sheetData>
@@ -31007,7 +31147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IY3"/>
+  <dimension ref="A1:IZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31269,6 +31409,7 @@
     <col width="12" customWidth="1" min="257" max="257"/>
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
+    <col width="12" customWidth="1" min="260" max="260"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32053,6 +32194,9 @@
       <c r="IY1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IZ1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32833,6 +32977,9 @@
       <c r="IY2" t="n">
         <v>311333</v>
       </c>
+      <c r="IZ2" t="n">
+        <v>493432</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33615,6 +33762,9 @@
       </c>
       <c r="IY3" t="n">
         <v>1382426</v>
+      </c>
+      <c r="IZ3" t="n">
+        <v>1567486</v>
       </c>
     </row>
   </sheetData>
@@ -33628,7 +33778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IF3"/>
+  <dimension ref="A1:IG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -33871,6 +34021,7 @@
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
+    <col width="10" customWidth="1" min="241" max="241"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34598,6 +34749,9 @@
       <c r="IF1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IG1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35324,6 +35478,9 @@
       <c r="IF2" t="n">
         <v>41</v>
       </c>
+      <c r="IG2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36049,6 +36206,9 @@
       </c>
       <c r="IF3" t="n">
         <v>36</v>
+      </c>
+      <c r="IG3" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -36062,7 +36222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GR3"/>
+  <dimension ref="A1:GS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36265,6 +36425,7 @@
     <col width="10" customWidth="1" min="198" max="198"/>
     <col width="10" customWidth="1" min="199" max="199"/>
     <col width="10" customWidth="1" min="200" max="200"/>
+    <col width="10" customWidth="1" min="201" max="201"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36872,6 +37033,9 @@
       <c r="GR1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="GS1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37478,6 +37642,9 @@
       <c r="GR2" t="n">
         <v>67</v>
       </c>
+      <c r="GS2" t="n">
+        <v>61</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38083,6 +38250,9 @@
       </c>
       <c r="GR3" t="n">
         <v>52</v>
+      </c>
+      <c r="GS3" t="n">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -38096,7 +38266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IF3"/>
+  <dimension ref="A1:IG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38339,6 +38509,7 @@
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
+    <col width="10" customWidth="1" min="241" max="241"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39066,6 +39237,9 @@
       <c r="IF1" s="1" t="n">
         <v>20260908</v>
       </c>
+      <c r="IG1" s="1" t="n">
+        <v>20260909</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39792,6 +39966,9 @@
       <c r="IF2" t="n">
         <v>8</v>
       </c>
+      <c r="IG2" t="n">
+        <v>-18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40517,6 +40694,9 @@
       </c>
       <c r="IF3" t="n">
         <v>-1</v>
+      </c>
+      <c r="IG3" t="n">
+        <v>-26</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS3"/>
+  <dimension ref="A1:GT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -726,6 +726,7 @@
     <col width="10" customWidth="1" min="199" max="199"/>
     <col width="10" customWidth="1" min="200" max="200"/>
     <col width="10" customWidth="1" min="201" max="201"/>
+    <col width="10" customWidth="1" min="202" max="202"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1336,6 +1337,9 @@
       <c r="GS1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="GT1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1945,6 +1949,9 @@
       <c r="GS2" t="n">
         <v>-1</v>
       </c>
+      <c r="GT2" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2553,6 +2560,9 @@
       </c>
       <c r="GS3" t="n">
         <v>-20</v>
+      </c>
+      <c r="GT3" t="n">
+        <v>-29</v>
       </c>
     </row>
   </sheetData>
@@ -2566,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IG3"/>
+  <dimension ref="A1:IH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2810,6 +2820,7 @@
     <col width="12" customWidth="1" min="239" max="239"/>
     <col width="12" customWidth="1" min="240" max="240"/>
     <col width="12" customWidth="1" min="241" max="241"/>
+    <col width="12" customWidth="1" min="242" max="242"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4018,6 +4029,11 @@
           <t>20260909</t>
         </is>
       </c>
+      <c r="IH1" s="1" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4687,6 +4703,9 @@
       <c r="IG2" t="n">
         <v>100</v>
       </c>
+      <c r="IH2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5415,6 +5434,9 @@
       </c>
       <c r="IG3" t="n">
         <v>98</v>
+      </c>
+      <c r="IH3" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5428,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HN3"/>
+  <dimension ref="A1:HO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5653,6 +5675,7 @@
     <col width="12" customWidth="1" min="220" max="220"/>
     <col width="12" customWidth="1" min="221" max="221"/>
     <col width="12" customWidth="1" min="222" max="222"/>
+    <col width="12" customWidth="1" min="223" max="223"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6766,6 +6789,11 @@
           <t>20260909</t>
         </is>
       </c>
+      <c r="HO1" s="1" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7321,6 +7349,9 @@
       <c r="HN2" t="n">
         <v>-44.13</v>
       </c>
+      <c r="HO2" t="n">
+        <v>-42.01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7992,6 +8023,9 @@
       </c>
       <c r="HN3" t="n">
         <v>-36.92</v>
+      </c>
+      <c r="HO3" t="n">
+        <v>-34.94</v>
       </c>
     </row>
   </sheetData>
@@ -8005,7 +8039,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS3"/>
+  <dimension ref="A1:GT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8209,6 +8243,7 @@
     <col width="12" customWidth="1" min="199" max="199"/>
     <col width="12" customWidth="1" min="200" max="200"/>
     <col width="12" customWidth="1" min="201" max="201"/>
+    <col width="12" customWidth="1" min="202" max="202"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9217,6 +9252,11 @@
           <t>20260909</t>
         </is>
       </c>
+      <c r="GT1" s="1" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9646,6 +9686,9 @@
       <c r="GS2" t="n">
         <v>6</v>
       </c>
+      <c r="GT2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10254,6 +10297,9 @@
       </c>
       <c r="GS3" t="n">
         <v>11</v>
+      </c>
+      <c r="GT3" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -10267,7 +10313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HW3"/>
+  <dimension ref="A1:HX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10501,6 +10547,7 @@
     <col width="10" customWidth="1" min="229" max="229"/>
     <col width="10" customWidth="1" min="230" max="230"/>
     <col width="10" customWidth="1" min="231" max="231"/>
+    <col width="10" customWidth="1" min="232" max="232"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11201,6 +11248,9 @@
       <c r="HW1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="HX1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11900,6 +11950,9 @@
       <c r="HW2" t="n">
         <v>3</v>
       </c>
+      <c r="HX2" t="n">
+        <v>-13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12598,6 +12651,9 @@
       </c>
       <c r="HW3" t="n">
         <v>-6</v>
+      </c>
+      <c r="HX3" t="n">
+        <v>-22</v>
       </c>
     </row>
   </sheetData>
@@ -12611,7 +12667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK3"/>
+  <dimension ref="A1:EL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12755,6 +12811,7 @@
     <col width="10" customWidth="1" min="139" max="139"/>
     <col width="10" customWidth="1" min="140" max="140"/>
     <col width="10" customWidth="1" min="141" max="141"/>
+    <col width="10" customWidth="1" min="142" max="142"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13185,6 +13242,9 @@
       <c r="EK1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="EL1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13614,6 +13674,9 @@
       <c r="EK2" t="n">
         <v>82</v>
       </c>
+      <c r="EL2" t="n">
+        <v>81</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14042,6 +14105,9 @@
       </c>
       <c r="EK3" t="n">
         <v>66</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -14055,7 +14121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EK3"/>
+  <dimension ref="A1:EL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14199,6 +14265,7 @@
     <col width="10" customWidth="1" min="139" max="139"/>
     <col width="10" customWidth="1" min="140" max="140"/>
     <col width="10" customWidth="1" min="141" max="141"/>
+    <col width="10" customWidth="1" min="142" max="142"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14629,6 +14696,9 @@
       <c r="EK1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="EL1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15058,6 +15128,9 @@
       <c r="EK2" t="n">
         <v>26</v>
       </c>
+      <c r="EL2" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15486,6 +15559,9 @@
       </c>
       <c r="EK3" t="n">
         <v>11</v>
+      </c>
+      <c r="EL3" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15499,7 +15575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS3"/>
+  <dimension ref="A1:GT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15703,6 +15779,7 @@
     <col width="12" customWidth="1" min="199" max="199"/>
     <col width="12" customWidth="1" min="200" max="200"/>
     <col width="12" customWidth="1" min="201" max="201"/>
+    <col width="12" customWidth="1" min="202" max="202"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16711,6 +16788,11 @@
           <t>20260909</t>
         </is>
       </c>
+      <c r="GT1" s="1" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17140,6 +17222,9 @@
       <c r="GS2" t="n">
         <v>100</v>
       </c>
+      <c r="GT2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17748,6 +17833,9 @@
       </c>
       <c r="GS3" t="n">
         <v>97</v>
+      </c>
+      <c r="GT3" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -17761,7 +17849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IG3"/>
+  <dimension ref="A1:IH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18005,6 +18093,7 @@
     <col width="12" customWidth="1" min="239" max="239"/>
     <col width="12" customWidth="1" min="240" max="240"/>
     <col width="12" customWidth="1" min="241" max="241"/>
+    <col width="12" customWidth="1" min="242" max="242"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19213,6 +19302,11 @@
           <t>20260909</t>
         </is>
       </c>
+      <c r="IH1" s="1" t="inlineStr">
+        <is>
+          <t>20260910</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19882,6 +19976,9 @@
       <c r="IG2" t="n">
         <v>7.7</v>
       </c>
+      <c r="IH2" t="n">
+        <v>7.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20610,6 +20707,9 @@
       </c>
       <c r="IG3" t="n">
         <v>2.49</v>
+      </c>
+      <c r="IH3" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -20623,7 +20723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IZ3"/>
+  <dimension ref="A1:JA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20886,6 +20986,7 @@
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21673,6 +21774,9 @@
       <c r="IZ1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="JA1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22456,6 +22560,9 @@
       <c r="IZ2" t="n">
         <v>719.58</v>
       </c>
+      <c r="JA2" t="n">
+        <v>716.1781999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23241,6 +23348,9 @@
       </c>
       <c r="IZ3" t="n">
         <v>72.51000000000001</v>
+      </c>
+      <c r="JA3" t="n">
+        <v>71.34999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23254,7 +23364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IZ3"/>
+  <dimension ref="A1:JA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23517,6 +23627,7 @@
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24304,6 +24415,9 @@
       <c r="IZ1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="JA1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25087,6 +25201,9 @@
       <c r="IZ2" t="n">
         <v>720.78</v>
       </c>
+      <c r="JA2" t="n">
+        <v>717.52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25872,6 +25989,9 @@
       </c>
       <c r="IZ3" t="n">
         <v>72.83</v>
+      </c>
+      <c r="JA3" t="n">
+        <v>71.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -25885,7 +26005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IZ3"/>
+  <dimension ref="A1:JA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26148,6 +26268,7 @@
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26935,6 +27056,9 @@
       <c r="IZ1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="JA1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27718,6 +27842,9 @@
       <c r="IZ2" t="n">
         <v>713.45</v>
       </c>
+      <c r="JA2" t="n">
+        <v>710.6799999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28503,6 +28630,9 @@
       </c>
       <c r="IZ3" t="n">
         <v>70.6699</v>
+      </c>
+      <c r="JA3" t="n">
+        <v>69.84</v>
       </c>
     </row>
   </sheetData>
@@ -28516,7 +28646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IZ3"/>
+  <dimension ref="A1:JA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28779,6 +28909,7 @@
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29566,6 +29697,9 @@
       <c r="IZ1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="JA1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30349,6 +30483,9 @@
       <c r="IZ2" t="n">
         <v>714.0739</v>
       </c>
+      <c r="JA2" t="n">
+        <v>710.88</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31134,6 +31271,9 @@
       </c>
       <c r="IZ3" t="n">
         <v>70.84</v>
+      </c>
+      <c r="JA3" t="n">
+        <v>69.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31147,7 +31287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IZ3"/>
+  <dimension ref="A1:JA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31410,6 +31550,7 @@
     <col width="12" customWidth="1" min="258" max="258"/>
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
+    <col width="12" customWidth="1" min="261" max="261"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32197,6 +32338,9 @@
       <c r="IZ1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="JA1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -32980,6 +33124,9 @@
       <c r="IZ2" t="n">
         <v>493432</v>
       </c>
+      <c r="JA2" t="n">
+        <v>403428</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33765,6 +33912,9 @@
       </c>
       <c r="IZ3" t="n">
         <v>1567486</v>
+      </c>
+      <c r="JA3" t="n">
+        <v>1656955</v>
       </c>
     </row>
   </sheetData>
@@ -33778,7 +33928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IG3"/>
+  <dimension ref="A1:IH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34022,6 +34172,7 @@
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
+    <col width="10" customWidth="1" min="242" max="242"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34752,6 +34903,9 @@
       <c r="IG1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="IH1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35481,6 +35635,9 @@
       <c r="IG2" t="n">
         <v>25</v>
       </c>
+      <c r="IH2" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36209,6 +36366,9 @@
       </c>
       <c r="IG3" t="n">
         <v>21</v>
+      </c>
+      <c r="IH3" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -36222,7 +36382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GS3"/>
+  <dimension ref="A1:GT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36426,6 +36586,7 @@
     <col width="10" customWidth="1" min="199" max="199"/>
     <col width="10" customWidth="1" min="200" max="200"/>
     <col width="10" customWidth="1" min="201" max="201"/>
+    <col width="10" customWidth="1" min="202" max="202"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37036,6 +37197,9 @@
       <c r="GS1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="GT1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37645,6 +37809,9 @@
       <c r="GS2" t="n">
         <v>61</v>
       </c>
+      <c r="GT2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38253,6 +38420,9 @@
       </c>
       <c r="GS3" t="n">
         <v>46</v>
+      </c>
+      <c r="GT3" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -38266,7 +38436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IG3"/>
+  <dimension ref="A1:IH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38510,6 +38680,7 @@
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
+    <col width="10" customWidth="1" min="242" max="242"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39240,6 +39411,9 @@
       <c r="IG1" s="1" t="n">
         <v>20260909</v>
       </c>
+      <c r="IH1" s="1" t="n">
+        <v>20260910</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39969,6 +40143,9 @@
       <c r="IG2" t="n">
         <v>-18</v>
       </c>
+      <c r="IH2" t="n">
+        <v>-35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40697,6 +40874,9 @@
       </c>
       <c r="IG3" t="n">
         <v>-26</v>
+      </c>
+      <c r="IH3" t="n">
+        <v>-40</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GT3"/>
+  <dimension ref="A1:GU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -727,6 +727,7 @@
     <col width="10" customWidth="1" min="200" max="200"/>
     <col width="10" customWidth="1" min="201" max="201"/>
     <col width="10" customWidth="1" min="202" max="202"/>
+    <col width="10" customWidth="1" min="203" max="203"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1340,6 +1341,9 @@
       <c r="GT1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="GU1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1952,6 +1956,9 @@
       <c r="GT2" t="n">
         <v>-10</v>
       </c>
+      <c r="GU2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2563,6 +2570,9 @@
       </c>
       <c r="GT3" t="n">
         <v>-29</v>
+      </c>
+      <c r="GU3" t="n">
+        <v>-19</v>
       </c>
     </row>
   </sheetData>
@@ -2576,7 +2586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IH3"/>
+  <dimension ref="A1:II3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2821,6 +2831,7 @@
     <col width="12" customWidth="1" min="240" max="240"/>
     <col width="12" customWidth="1" min="241" max="241"/>
     <col width="12" customWidth="1" min="242" max="242"/>
+    <col width="12" customWidth="1" min="243" max="243"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4034,6 +4045,11 @@
           <t>20260910</t>
         </is>
       </c>
+      <c r="II1" s="1" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4706,6 +4722,9 @@
       <c r="IH2" t="n">
         <v>99</v>
       </c>
+      <c r="II2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5437,6 +5456,9 @@
       </c>
       <c r="IH3" t="n">
         <v>97</v>
+      </c>
+      <c r="II3" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5450,7 +5472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HO3"/>
+  <dimension ref="A1:HP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5676,6 +5698,7 @@
     <col width="12" customWidth="1" min="221" max="221"/>
     <col width="12" customWidth="1" min="222" max="222"/>
     <col width="12" customWidth="1" min="223" max="223"/>
+    <col width="12" customWidth="1" min="224" max="224"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6794,6 +6817,11 @@
           <t>20260910</t>
         </is>
       </c>
+      <c r="HP1" s="1" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7352,6 +7380,9 @@
       <c r="HO2" t="n">
         <v>-42.01</v>
       </c>
+      <c r="HP2" t="n">
+        <v>-41.16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8026,6 +8057,9 @@
       </c>
       <c r="HO3" t="n">
         <v>-34.94</v>
+      </c>
+      <c r="HP3" t="n">
+        <v>-34.65</v>
       </c>
     </row>
   </sheetData>
@@ -8039,7 +8073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GT3"/>
+  <dimension ref="A1:GU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8244,6 +8278,7 @@
     <col width="12" customWidth="1" min="200" max="200"/>
     <col width="12" customWidth="1" min="201" max="201"/>
     <col width="12" customWidth="1" min="202" max="202"/>
+    <col width="12" customWidth="1" min="203" max="203"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9257,6 +9292,11 @@
           <t>20260910</t>
         </is>
       </c>
+      <c r="GU1" s="1" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9689,6 +9729,9 @@
       <c r="GT2" t="n">
         <v>6</v>
       </c>
+      <c r="GU2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10300,6 +10343,9 @@
       </c>
       <c r="GT3" t="n">
         <v>14</v>
+      </c>
+      <c r="GU3" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -10313,7 +10359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HX3"/>
+  <dimension ref="A1:HY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10548,6 +10594,7 @@
     <col width="10" customWidth="1" min="230" max="230"/>
     <col width="10" customWidth="1" min="231" max="231"/>
     <col width="10" customWidth="1" min="232" max="232"/>
+    <col width="10" customWidth="1" min="233" max="233"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11251,6 +11298,9 @@
       <c r="HX1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="HY1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -11953,6 +12003,9 @@
       <c r="HX2" t="n">
         <v>-13</v>
       </c>
+      <c r="HY2" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12653,6 +12706,9 @@
         <v>-6</v>
       </c>
       <c r="HX3" t="n">
+        <v>-22</v>
+      </c>
+      <c r="HY3" t="n">
         <v>-22</v>
       </c>
     </row>
@@ -12667,7 +12723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL3"/>
+  <dimension ref="A1:EM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12812,6 +12868,7 @@
     <col width="10" customWidth="1" min="140" max="140"/>
     <col width="10" customWidth="1" min="141" max="141"/>
     <col width="10" customWidth="1" min="142" max="142"/>
+    <col width="10" customWidth="1" min="143" max="143"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13245,6 +13302,9 @@
       <c r="EL1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="EM1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13677,6 +13737,9 @@
       <c r="EL2" t="n">
         <v>81</v>
       </c>
+      <c r="EM2" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14108,6 +14171,9 @@
       </c>
       <c r="EL3" t="n">
         <v>64</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -14121,7 +14187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL3"/>
+  <dimension ref="A1:EM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14266,6 +14332,7 @@
     <col width="10" customWidth="1" min="140" max="140"/>
     <col width="10" customWidth="1" min="141" max="141"/>
     <col width="10" customWidth="1" min="142" max="142"/>
+    <col width="10" customWidth="1" min="143" max="143"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14699,6 +14766,9 @@
       <c r="EL1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="EM1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15131,6 +15201,9 @@
       <c r="EL2" t="n">
         <v>22</v>
       </c>
+      <c r="EM2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15562,6 +15635,9 @@
       </c>
       <c r="EL3" t="n">
         <v>7</v>
+      </c>
+      <c r="EM3" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15575,7 +15651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GT3"/>
+  <dimension ref="A1:GU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15780,6 +15856,7 @@
     <col width="12" customWidth="1" min="200" max="200"/>
     <col width="12" customWidth="1" min="201" max="201"/>
     <col width="12" customWidth="1" min="202" max="202"/>
+    <col width="12" customWidth="1" min="203" max="203"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16793,6 +16870,11 @@
           <t>20260910</t>
         </is>
       </c>
+      <c r="GU1" s="1" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17225,6 +17307,9 @@
       <c r="GT2" t="n">
         <v>100</v>
       </c>
+      <c r="GU2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17836,6 +17921,9 @@
       </c>
       <c r="GT3" t="n">
         <v>96</v>
+      </c>
+      <c r="GU3" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -17849,7 +17937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IH3"/>
+  <dimension ref="A1:II3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18094,6 +18182,7 @@
     <col width="12" customWidth="1" min="240" max="240"/>
     <col width="12" customWidth="1" min="241" max="241"/>
     <col width="12" customWidth="1" min="242" max="242"/>
+    <col width="12" customWidth="1" min="243" max="243"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19307,6 +19396,11 @@
           <t>20260910</t>
         </is>
       </c>
+      <c r="II1" s="1" t="inlineStr">
+        <is>
+          <t>20260911</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -19979,6 +20073,9 @@
       <c r="IH2" t="n">
         <v>7.73</v>
       </c>
+      <c r="II2" t="n">
+        <v>7.56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20710,6 +20807,9 @@
       </c>
       <c r="IH3" t="n">
         <v>2.5</v>
+      </c>
+      <c r="II3" t="n">
+        <v>2.44</v>
       </c>
     </row>
   </sheetData>
@@ -20723,7 +20823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JA3"/>
+  <dimension ref="A1:JB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -20987,6 +21087,7 @@
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21777,6 +21878,9 @@
       <c r="JA1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="JB1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22563,6 +22667,9 @@
       <c r="JA2" t="n">
         <v>716.1781999999999</v>
       </c>
+      <c r="JB2" t="n">
+        <v>711.0599999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23351,6 +23458,9 @@
       </c>
       <c r="JA3" t="n">
         <v>71.34999999999999</v>
+      </c>
+      <c r="JB3" t="n">
+        <v>69.98</v>
       </c>
     </row>
   </sheetData>
@@ -23364,7 +23474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JA3"/>
+  <dimension ref="A1:JB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23628,6 +23738,7 @@
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24418,6 +24529,9 @@
       <c r="JA1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="JB1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25204,6 +25318,9 @@
       <c r="JA2" t="n">
         <v>717.52</v>
       </c>
+      <c r="JB2" t="n">
+        <v>713.9400000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -25992,6 +26109,9 @@
       </c>
       <c r="JA3" t="n">
         <v>71.90000000000001</v>
+      </c>
+      <c r="JB3" t="n">
+        <v>70.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -26005,7 +26125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JA3"/>
+  <dimension ref="A1:JB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26269,6 +26389,7 @@
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27059,6 +27180,9 @@
       <c r="JA1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="JB1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27845,6 +27969,9 @@
       <c r="JA2" t="n">
         <v>710.6799999999999</v>
       </c>
+      <c r="JB2" t="n">
+        <v>706.5599999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28633,6 +28760,9 @@
       </c>
       <c r="JA3" t="n">
         <v>69.84</v>
+      </c>
+      <c r="JB3" t="n">
+        <v>68.54000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -28646,7 +28776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JA3"/>
+  <dimension ref="A1:JB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -28910,6 +29040,7 @@
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29700,6 +29831,9 @@
       <c r="JA1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="JB1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30486,6 +30620,9 @@
       <c r="JA2" t="n">
         <v>710.88</v>
       </c>
+      <c r="JB2" t="n">
+        <v>713.7603</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31274,6 +31411,9 @@
       </c>
       <c r="JA3" t="n">
         <v>69.90000000000001</v>
+      </c>
+      <c r="JB3" t="n">
+        <v>70.6417</v>
       </c>
     </row>
   </sheetData>
@@ -31287,7 +31427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JA3"/>
+  <dimension ref="A1:JB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31551,6 +31691,7 @@
     <col width="12" customWidth="1" min="259" max="259"/>
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
+    <col width="12" customWidth="1" min="262" max="262"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32341,6 +32482,9 @@
       <c r="JA1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="JB1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33127,6 +33271,9 @@
       <c r="JA2" t="n">
         <v>403428</v>
       </c>
+      <c r="JB2" t="n">
+        <v>313993</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -33915,6 +34062,9 @@
       </c>
       <c r="JA3" t="n">
         <v>1656955</v>
+      </c>
+      <c r="JB3" t="n">
+        <v>1440573</v>
       </c>
     </row>
   </sheetData>
@@ -33928,7 +34078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IH3"/>
+  <dimension ref="A1:II3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34173,6 +34323,7 @@
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
     <col width="10" customWidth="1" min="242" max="242"/>
+    <col width="10" customWidth="1" min="243" max="243"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -34906,6 +35057,9 @@
       <c r="IH1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="II1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35638,6 +35792,9 @@
       <c r="IH2" t="n">
         <v>14</v>
       </c>
+      <c r="II2" t="n">
+        <v>24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36369,6 +36526,9 @@
       </c>
       <c r="IH3" t="n">
         <v>10</v>
+      </c>
+      <c r="II3" t="n">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -36382,7 +36542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GT3"/>
+  <dimension ref="A1:GU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36587,6 +36747,7 @@
     <col width="10" customWidth="1" min="200" max="200"/>
     <col width="10" customWidth="1" min="201" max="201"/>
     <col width="10" customWidth="1" min="202" max="202"/>
+    <col width="10" customWidth="1" min="203" max="203"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37200,6 +37361,9 @@
       <c r="GT1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="GU1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37812,6 +37976,9 @@
       <c r="GT2" t="n">
         <v>60</v>
       </c>
+      <c r="GU2" t="n">
+        <v>64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38423,6 +38590,9 @@
       </c>
       <c r="GT3" t="n">
         <v>45</v>
+      </c>
+      <c r="GU3" t="n">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -38436,7 +38606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IH3"/>
+  <dimension ref="A1:II3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38681,6 +38851,7 @@
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
     <col width="10" customWidth="1" min="242" max="242"/>
+    <col width="10" customWidth="1" min="243" max="243"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39414,6 +39585,9 @@
       <c r="IH1" s="1" t="n">
         <v>20260910</v>
       </c>
+      <c r="II1" s="1" t="n">
+        <v>20260911</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40146,6 +40320,9 @@
       <c r="IH2" t="n">
         <v>-35</v>
       </c>
+      <c r="II2" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40877,6 +41054,9 @@
       </c>
       <c r="IH3" t="n">
         <v>-40</v>
+      </c>
+      <c r="II3" t="n">
+        <v>-22</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU3"/>
+  <dimension ref="A1:GV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -728,6 +728,7 @@
     <col width="10" customWidth="1" min="201" max="201"/>
     <col width="10" customWidth="1" min="202" max="202"/>
     <col width="10" customWidth="1" min="203" max="203"/>
+    <col width="10" customWidth="1" min="204" max="204"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1344,6 +1345,9 @@
       <c r="GU1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="GV1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1959,6 +1963,9 @@
       <c r="GU2" t="n">
         <v>1</v>
       </c>
+      <c r="GV2" t="n">
+        <v>-20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2573,6 +2580,9 @@
       </c>
       <c r="GU3" t="n">
         <v>-19</v>
+      </c>
+      <c r="GV3" t="n">
+        <v>-39</v>
       </c>
     </row>
   </sheetData>
@@ -2586,7 +2596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:II3"/>
+  <dimension ref="A1:IJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2832,6 +2842,7 @@
     <col width="12" customWidth="1" min="241" max="241"/>
     <col width="12" customWidth="1" min="242" max="242"/>
     <col width="12" customWidth="1" min="243" max="243"/>
+    <col width="12" customWidth="1" min="244" max="244"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4050,6 +4061,11 @@
           <t>20260911</t>
         </is>
       </c>
+      <c r="IJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4725,6 +4741,9 @@
       <c r="II2" t="n">
         <v>100</v>
       </c>
+      <c r="IJ2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5459,6 +5478,9 @@
       </c>
       <c r="II3" t="n">
         <v>98</v>
+      </c>
+      <c r="IJ3" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -5472,7 +5494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HP3"/>
+  <dimension ref="A1:HQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5699,6 +5721,7 @@
     <col width="12" customWidth="1" min="222" max="222"/>
     <col width="12" customWidth="1" min="223" max="223"/>
     <col width="12" customWidth="1" min="224" max="224"/>
+    <col width="12" customWidth="1" min="225" max="225"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6822,6 +6845,11 @@
           <t>20260911</t>
         </is>
       </c>
+      <c r="HQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7383,6 +7411,9 @@
       <c r="HP2" t="n">
         <v>-41.16</v>
       </c>
+      <c r="HQ2" t="n">
+        <v>-45.74</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8060,6 +8091,9 @@
       </c>
       <c r="HP3" t="n">
         <v>-34.65</v>
+      </c>
+      <c r="HQ3" t="n">
+        <v>-40.29</v>
       </c>
     </row>
   </sheetData>
@@ -8073,7 +8107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU3"/>
+  <dimension ref="A1:GV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8279,6 +8313,7 @@
     <col width="12" customWidth="1" min="201" max="201"/>
     <col width="12" customWidth="1" min="202" max="202"/>
     <col width="12" customWidth="1" min="203" max="203"/>
+    <col width="12" customWidth="1" min="204" max="204"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9297,6 +9332,11 @@
           <t>20260911</t>
         </is>
       </c>
+      <c r="GV1" s="1" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9732,6 +9772,9 @@
       <c r="GU2" t="n">
         <v>5</v>
       </c>
+      <c r="GV2" t="n">
+        <v>90</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10346,6 +10389,9 @@
       </c>
       <c r="GU3" t="n">
         <v>15</v>
+      </c>
+      <c r="GV3" t="n">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -10359,7 +10405,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HY3"/>
+  <dimension ref="A1:HZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10595,6 +10641,7 @@
     <col width="10" customWidth="1" min="231" max="231"/>
     <col width="10" customWidth="1" min="232" max="232"/>
     <col width="10" customWidth="1" min="233" max="233"/>
+    <col width="10" customWidth="1" min="234" max="234"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11301,6 +11348,9 @@
       <c r="HY1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="HZ1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12006,6 +12056,9 @@
       <c r="HY2" t="n">
         <v>-10</v>
       </c>
+      <c r="HZ2" t="n">
+        <v>-52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12710,6 +12763,9 @@
       </c>
       <c r="HY3" t="n">
         <v>-22</v>
+      </c>
+      <c r="HZ3" t="n">
+        <v>-61</v>
       </c>
     </row>
   </sheetData>
@@ -12723,7 +12779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM3"/>
+  <dimension ref="A1:EN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12869,6 +12925,7 @@
     <col width="10" customWidth="1" min="141" max="141"/>
     <col width="10" customWidth="1" min="142" max="142"/>
     <col width="10" customWidth="1" min="143" max="143"/>
+    <col width="10" customWidth="1" min="144" max="144"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13305,6 +13362,9 @@
       <c r="EM1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="EN1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13740,6 +13800,9 @@
       <c r="EM2" t="n">
         <v>82</v>
       </c>
+      <c r="EN2" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14174,6 +14237,9 @@
       </c>
       <c r="EM3" t="n">
         <v>66</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -14187,7 +14253,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EM3"/>
+  <dimension ref="A1:EN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14333,6 +14399,7 @@
     <col width="10" customWidth="1" min="141" max="141"/>
     <col width="10" customWidth="1" min="142" max="142"/>
     <col width="10" customWidth="1" min="143" max="143"/>
+    <col width="10" customWidth="1" min="144" max="144"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14769,6 +14836,9 @@
       <c r="EM1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="EN1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15204,6 +15274,9 @@
       <c r="EM2" t="n">
         <v>24</v>
       </c>
+      <c r="EN2" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15638,6 +15711,9 @@
       </c>
       <c r="EM3" t="n">
         <v>9</v>
+      </c>
+      <c r="EN3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15651,7 +15727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU3"/>
+  <dimension ref="A1:GV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15857,6 +15933,7 @@
     <col width="12" customWidth="1" min="201" max="201"/>
     <col width="12" customWidth="1" min="202" max="202"/>
     <col width="12" customWidth="1" min="203" max="203"/>
+    <col width="12" customWidth="1" min="204" max="204"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16875,6 +16952,11 @@
           <t>20260911</t>
         </is>
       </c>
+      <c r="GV1" s="1" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17310,6 +17392,9 @@
       <c r="GU2" t="n">
         <v>100</v>
       </c>
+      <c r="GV2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -17924,6 +18009,9 @@
       </c>
       <c r="GU3" t="n">
         <v>98</v>
+      </c>
+      <c r="GV3" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -17937,7 +18025,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:II3"/>
+  <dimension ref="A1:IJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18183,6 +18271,7 @@
     <col width="12" customWidth="1" min="241" max="241"/>
     <col width="12" customWidth="1" min="242" max="242"/>
     <col width="12" customWidth="1" min="243" max="243"/>
+    <col width="12" customWidth="1" min="244" max="244"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19401,6 +19490,11 @@
           <t>20260911</t>
         </is>
       </c>
+      <c r="IJ1" s="1" t="inlineStr">
+        <is>
+          <t>20260914</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20076,6 +20170,9 @@
       <c r="II2" t="n">
         <v>7.56</v>
       </c>
+      <c r="IJ2" t="n">
+        <v>6.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20810,6 +20907,9 @@
       </c>
       <c r="II3" t="n">
         <v>2.44</v>
+      </c>
+      <c r="IJ3" t="n">
+        <v>2.14</v>
       </c>
     </row>
   </sheetData>
@@ -20823,7 +20923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JB3"/>
+  <dimension ref="A1:JC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21088,6 +21188,7 @@
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21881,6 +21982,9 @@
       <c r="JB1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="JC1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22670,6 +22774,9 @@
       <c r="JB2" t="n">
         <v>711.0599999999999</v>
       </c>
+      <c r="JC2" t="n">
+        <v>703.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23461,6 +23568,9 @@
       </c>
       <c r="JB3" t="n">
         <v>69.98</v>
+      </c>
+      <c r="JC3" t="n">
+        <v>67.53</v>
       </c>
     </row>
   </sheetData>
@@ -23474,7 +23584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JB3"/>
+  <dimension ref="A1:JC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23739,6 +23849,7 @@
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24532,6 +24643,9 @@
       <c r="JB1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="JC1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25321,6 +25435,9 @@
       <c r="JB2" t="n">
         <v>713.9400000000001</v>
       </c>
+      <c r="JC2" t="n">
+        <v>707.7699</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26112,6 +26229,9 @@
       </c>
       <c r="JB3" t="n">
         <v>70.70999999999999</v>
+      </c>
+      <c r="JC3" t="n">
+        <v>68.8395</v>
       </c>
     </row>
   </sheetData>
@@ -26125,7 +26245,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JB3"/>
+  <dimension ref="A1:JC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26390,6 +26510,7 @@
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27183,6 +27304,9 @@
       <c r="JB1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="JC1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -27972,6 +28096,9 @@
       <c r="JB2" t="n">
         <v>706.5599999999999</v>
       </c>
+      <c r="JC2" t="n">
+        <v>702.75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28763,6 +28890,9 @@
       </c>
       <c r="JB3" t="n">
         <v>68.54000000000001</v>
+      </c>
+      <c r="JC3" t="n">
+        <v>67.34</v>
       </c>
     </row>
   </sheetData>
@@ -28776,7 +28906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JB3"/>
+  <dimension ref="A1:JC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29041,6 +29171,7 @@
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29834,6 +29965,9 @@
       <c r="JB1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="JC1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30623,6 +30757,9 @@
       <c r="JB2" t="n">
         <v>713.7603</v>
       </c>
+      <c r="JC2" t="n">
+        <v>707.4299999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31414,6 +31551,9 @@
       </c>
       <c r="JB3" t="n">
         <v>70.6417</v>
+      </c>
+      <c r="JC3" t="n">
+        <v>68.72750000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31427,7 +31567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JB3"/>
+  <dimension ref="A1:JC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31692,6 +31832,7 @@
     <col width="12" customWidth="1" min="260" max="260"/>
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32485,6 +32626,9 @@
       <c r="JB1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="JC1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33274,6 +33418,9 @@
       <c r="JB2" t="n">
         <v>313993</v>
       </c>
+      <c r="JC2" t="n">
+        <v>5365819</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34065,6 +34212,9 @@
       </c>
       <c r="JB3" t="n">
         <v>1440573</v>
+      </c>
+      <c r="JC3" t="n">
+        <v>12250797</v>
       </c>
     </row>
   </sheetData>
@@ -34078,7 +34228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:II3"/>
+  <dimension ref="A1:IJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34324,6 +34474,7 @@
     <col width="10" customWidth="1" min="241" max="241"/>
     <col width="10" customWidth="1" min="242" max="242"/>
     <col width="10" customWidth="1" min="243" max="243"/>
+    <col width="10" customWidth="1" min="244" max="244"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35060,6 +35211,9 @@
       <c r="II1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="IJ1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35795,6 +35949,9 @@
       <c r="II2" t="n">
         <v>24</v>
       </c>
+      <c r="IJ2" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36529,6 +36686,9 @@
       </c>
       <c r="II3" t="n">
         <v>19</v>
+      </c>
+      <c r="IJ3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -36542,7 +36702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GU3"/>
+  <dimension ref="A1:GV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36748,6 +36908,7 @@
     <col width="10" customWidth="1" min="201" max="201"/>
     <col width="10" customWidth="1" min="202" max="202"/>
     <col width="10" customWidth="1" min="203" max="203"/>
+    <col width="10" customWidth="1" min="204" max="204"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37364,6 +37525,9 @@
       <c r="GU1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="GV1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37979,6 +38143,9 @@
       <c r="GU2" t="n">
         <v>64</v>
       </c>
+      <c r="GV2" t="n">
+        <v>55</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38593,6 +38760,9 @@
       </c>
       <c r="GU3" t="n">
         <v>48</v>
+      </c>
+      <c r="GV3" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -38606,7 +38776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:II3"/>
+  <dimension ref="A1:IJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38852,6 +39022,7 @@
     <col width="10" customWidth="1" min="241" max="241"/>
     <col width="10" customWidth="1" min="242" max="242"/>
     <col width="10" customWidth="1" min="243" max="243"/>
+    <col width="10" customWidth="1" min="244" max="244"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39588,6 +39759,9 @@
       <c r="II1" s="1" t="n">
         <v>20260911</v>
       </c>
+      <c r="IJ1" s="1" t="n">
+        <v>20260914</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40323,6 +40497,9 @@
       <c r="II2" t="n">
         <v>-14</v>
       </c>
+      <c r="IJ2" t="n">
+        <v>-53</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41057,6 +41234,9 @@
       </c>
       <c r="II3" t="n">
         <v>-22</v>
+      </c>
+      <c r="IJ3" t="n">
+        <v>-59</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV3"/>
+  <dimension ref="A1:GW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,7 @@
     <col width="10" customWidth="1" min="202" max="202"/>
     <col width="10" customWidth="1" min="203" max="203"/>
     <col width="10" customWidth="1" min="204" max="204"/>
+    <col width="10" customWidth="1" min="205" max="205"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1348,6 +1349,9 @@
       <c r="GV1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="GW1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1966,6 +1970,9 @@
       <c r="GV2" t="n">
         <v>-20</v>
       </c>
+      <c r="GW2" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2583,6 +2590,9 @@
       </c>
       <c r="GV3" t="n">
         <v>-39</v>
+      </c>
+      <c r="GW3" t="n">
+        <v>-33</v>
       </c>
     </row>
   </sheetData>
@@ -2596,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IJ3"/>
+  <dimension ref="A1:IK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2843,6 +2853,7 @@
     <col width="12" customWidth="1" min="242" max="242"/>
     <col width="12" customWidth="1" min="243" max="243"/>
     <col width="12" customWidth="1" min="244" max="244"/>
+    <col width="12" customWidth="1" min="245" max="245"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4066,6 +4077,11 @@
           <t>20260914</t>
         </is>
       </c>
+      <c r="IK1" s="1" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4744,6 +4760,9 @@
       <c r="IJ2" t="n">
         <v>99</v>
       </c>
+      <c r="IK2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5481,6 +5500,9 @@
       </c>
       <c r="IJ3" t="n">
         <v>96</v>
+      </c>
+      <c r="IK3" t="n">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -5494,7 +5516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HQ3"/>
+  <dimension ref="A1:HR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5722,6 +5744,7 @@
     <col width="12" customWidth="1" min="223" max="223"/>
     <col width="12" customWidth="1" min="224" max="224"/>
     <col width="12" customWidth="1" min="225" max="225"/>
+    <col width="12" customWidth="1" min="226" max="226"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6850,6 +6873,11 @@
           <t>20260914</t>
         </is>
       </c>
+      <c r="HR1" s="1" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7414,6 +7442,9 @@
       <c r="HQ2" t="n">
         <v>-45.74</v>
       </c>
+      <c r="HR2" t="n">
+        <v>-58.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8094,6 +8125,9 @@
       </c>
       <c r="HQ3" t="n">
         <v>-40.29</v>
+      </c>
+      <c r="HR3" t="n">
+        <v>-54.61</v>
       </c>
     </row>
   </sheetData>
@@ -8107,7 +8141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV3"/>
+  <dimension ref="A1:GW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8314,6 +8348,7 @@
     <col width="12" customWidth="1" min="202" max="202"/>
     <col width="12" customWidth="1" min="203" max="203"/>
     <col width="12" customWidth="1" min="204" max="204"/>
+    <col width="12" customWidth="1" min="205" max="205"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9337,6 +9372,11 @@
           <t>20260914</t>
         </is>
       </c>
+      <c r="GW1" s="1" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9775,6 +9815,9 @@
       <c r="GV2" t="n">
         <v>90</v>
       </c>
+      <c r="GW2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10392,6 +10435,9 @@
       </c>
       <c r="GV3" t="n">
         <v>119</v>
+      </c>
+      <c r="GW3" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -10405,7 +10451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HZ3"/>
+  <dimension ref="A1:IA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10642,6 +10688,7 @@
     <col width="10" customWidth="1" min="232" max="232"/>
     <col width="10" customWidth="1" min="233" max="233"/>
     <col width="10" customWidth="1" min="234" max="234"/>
+    <col width="10" customWidth="1" min="235" max="235"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11351,6 +11398,9 @@
       <c r="HZ1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="IA1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12059,6 +12109,9 @@
       <c r="HZ2" t="n">
         <v>-52</v>
       </c>
+      <c r="IA2" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12766,6 +12819,9 @@
       </c>
       <c r="HZ3" t="n">
         <v>-61</v>
+      </c>
+      <c r="IA3" t="n">
+        <v>-60</v>
       </c>
     </row>
   </sheetData>
@@ -12779,7 +12835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EN3"/>
+  <dimension ref="A1:EO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12926,6 +12982,7 @@
     <col width="10" customWidth="1" min="142" max="142"/>
     <col width="10" customWidth="1" min="143" max="143"/>
     <col width="10" customWidth="1" min="144" max="144"/>
+    <col width="10" customWidth="1" min="145" max="145"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13365,6 +13422,9 @@
       <c r="EN1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="EO1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13803,6 +13863,9 @@
       <c r="EN2" t="n">
         <v>79</v>
       </c>
+      <c r="EO2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14240,6 +14303,9 @@
       </c>
       <c r="EN3" t="n">
         <v>62</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -14253,7 +14319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EN3"/>
+  <dimension ref="A1:EO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14400,6 +14466,7 @@
     <col width="10" customWidth="1" min="142" max="142"/>
     <col width="10" customWidth="1" min="143" max="143"/>
     <col width="10" customWidth="1" min="144" max="144"/>
+    <col width="10" customWidth="1" min="145" max="145"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14839,6 +14906,9 @@
       <c r="EN1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="EO1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15277,6 +15347,9 @@
       <c r="EN2" t="n">
         <v>17</v>
       </c>
+      <c r="EO2" t="n">
+        <v>18</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15714,6 +15787,9 @@
       </c>
       <c r="EN3" t="n">
         <v>0</v>
+      </c>
+      <c r="EO3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -15727,7 +15803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV3"/>
+  <dimension ref="A1:GW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15934,6 +16010,7 @@
     <col width="12" customWidth="1" min="202" max="202"/>
     <col width="12" customWidth="1" min="203" max="203"/>
     <col width="12" customWidth="1" min="204" max="204"/>
+    <col width="12" customWidth="1" min="205" max="205"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16957,6 +17034,11 @@
           <t>20260914</t>
         </is>
       </c>
+      <c r="GW1" s="1" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17395,6 +17477,9 @@
       <c r="GV2" t="n">
         <v>99</v>
       </c>
+      <c r="GW2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18012,6 +18097,9 @@
       </c>
       <c r="GV3" t="n">
         <v>95</v>
+      </c>
+      <c r="GW3" t="n">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -18025,7 +18113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IJ3"/>
+  <dimension ref="A1:IK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18272,6 +18360,7 @@
     <col width="12" customWidth="1" min="242" max="242"/>
     <col width="12" customWidth="1" min="243" max="243"/>
     <col width="12" customWidth="1" min="244" max="244"/>
+    <col width="12" customWidth="1" min="245" max="245"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19495,6 +19584,11 @@
           <t>20260914</t>
         </is>
       </c>
+      <c r="IK1" s="1" t="inlineStr">
+        <is>
+          <t>20260915</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20173,6 +20267,9 @@
       <c r="IJ2" t="n">
         <v>6.65</v>
       </c>
+      <c r="IK2" t="n">
+        <v>4.83</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -20910,6 +21007,9 @@
       </c>
       <c r="IJ3" t="n">
         <v>2.14</v>
+      </c>
+      <c r="IK3" t="n">
+        <v>1.54</v>
       </c>
     </row>
   </sheetData>
@@ -20923,7 +21023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC3"/>
+  <dimension ref="A1:JD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21189,6 +21289,7 @@
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21985,6 +22086,9 @@
       <c r="JC1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="JD1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22777,6 +22881,9 @@
       <c r="JC2" t="n">
         <v>703.29</v>
       </c>
+      <c r="JD2" t="n">
+        <v>706.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23571,6 +23678,9 @@
       </c>
       <c r="JC3" t="n">
         <v>67.53</v>
+      </c>
+      <c r="JD3" t="n">
+        <v>68.37</v>
       </c>
     </row>
   </sheetData>
@@ -23584,7 +23694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC3"/>
+  <dimension ref="A1:JD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23850,6 +23960,7 @@
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24646,6 +24757,9 @@
       <c r="JC1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="JD1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25438,6 +25552,9 @@
       <c r="JC2" t="n">
         <v>707.7699</v>
       </c>
+      <c r="JD2" t="n">
+        <v>712.52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26232,6 +26349,9 @@
       </c>
       <c r="JC3" t="n">
         <v>68.8395</v>
+      </c>
+      <c r="JD3" t="n">
+        <v>69.27</v>
       </c>
     </row>
   </sheetData>
@@ -26245,7 +26365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC3"/>
+  <dimension ref="A1:JD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26511,6 +26631,7 @@
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27307,6 +27428,9 @@
       <c r="JC1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="JD1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28099,6 +28223,9 @@
       <c r="JC2" t="n">
         <v>702.75</v>
       </c>
+      <c r="JD2" t="n">
+        <v>703.21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -28893,6 +29020,9 @@
       </c>
       <c r="JC3" t="n">
         <v>67.34</v>
+      </c>
+      <c r="JD3" t="n">
+        <v>67.78</v>
       </c>
     </row>
   </sheetData>
@@ -28906,7 +29036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC3"/>
+  <dimension ref="A1:JD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29172,6 +29302,7 @@
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29968,6 +30099,9 @@
       <c r="JC1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="JD1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30760,6 +30894,9 @@
       <c r="JC2" t="n">
         <v>707.4299999999999</v>
       </c>
+      <c r="JD2" t="n">
+        <v>708.98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31554,6 +31691,9 @@
       </c>
       <c r="JC3" t="n">
         <v>68.72750000000001</v>
+      </c>
+      <c r="JD3" t="n">
+        <v>69.19889999999999</v>
       </c>
     </row>
   </sheetData>
@@ -31567,7 +31707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JC3"/>
+  <dimension ref="A1:JD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31833,6 +31973,7 @@
     <col width="12" customWidth="1" min="261" max="261"/>
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
+    <col width="12" customWidth="1" min="264" max="264"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32629,6 +32770,9 @@
       <c r="JC1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="JD1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33421,6 +33565,9 @@
       <c r="JC2" t="n">
         <v>5365819</v>
       </c>
+      <c r="JD2" t="n">
+        <v>353460</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34215,6 +34362,9 @@
       </c>
       <c r="JC3" t="n">
         <v>12250797</v>
+      </c>
+      <c r="JD3" t="n">
+        <v>1559967</v>
       </c>
     </row>
   </sheetData>
@@ -34228,7 +34378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IJ3"/>
+  <dimension ref="A1:IK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34475,6 +34625,7 @@
     <col width="10" customWidth="1" min="242" max="242"/>
     <col width="10" customWidth="1" min="243" max="243"/>
     <col width="10" customWidth="1" min="244" max="244"/>
+    <col width="10" customWidth="1" min="245" max="245"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35214,6 +35365,9 @@
       <c r="IJ1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="IK1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -35952,6 +36106,9 @@
       <c r="IJ2" t="n">
         <v>1</v>
       </c>
+      <c r="IK2" t="n">
+        <v>12</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36689,6 +36846,9 @@
       </c>
       <c r="IJ3" t="n">
         <v>0</v>
+      </c>
+      <c r="IK3" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -36702,7 +36862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GV3"/>
+  <dimension ref="A1:GW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -36909,6 +37069,7 @@
     <col width="10" customWidth="1" min="202" max="202"/>
     <col width="10" customWidth="1" min="203" max="203"/>
     <col width="10" customWidth="1" min="204" max="204"/>
+    <col width="10" customWidth="1" min="205" max="205"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37528,6 +37689,9 @@
       <c r="GV1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="GW1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38146,6 +38310,9 @@
       <c r="GV2" t="n">
         <v>55</v>
       </c>
+      <c r="GW2" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38763,6 +38930,9 @@
       </c>
       <c r="GV3" t="n">
         <v>40</v>
+      </c>
+      <c r="GW3" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -38776,7 +38946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IJ3"/>
+  <dimension ref="A1:IK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39023,6 +39193,7 @@
     <col width="10" customWidth="1" min="242" max="242"/>
     <col width="10" customWidth="1" min="243" max="243"/>
     <col width="10" customWidth="1" min="244" max="244"/>
+    <col width="10" customWidth="1" min="245" max="245"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39762,6 +39933,9 @@
       <c r="IJ1" s="1" t="n">
         <v>20260914</v>
       </c>
+      <c r="IK1" s="1" t="n">
+        <v>20260915</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40500,6 +40674,9 @@
       <c r="IJ2" t="n">
         <v>-53</v>
       </c>
+      <c r="IK2" t="n">
+        <v>-44</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41237,6 +41414,9 @@
       </c>
       <c r="IJ3" t="n">
         <v>-59</v>
+      </c>
+      <c r="IK3" t="n">
+        <v>-53</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GW3"/>
+  <dimension ref="A1:GX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -730,6 +730,7 @@
     <col width="10" customWidth="1" min="203" max="203"/>
     <col width="10" customWidth="1" min="204" max="204"/>
     <col width="10" customWidth="1" min="205" max="205"/>
+    <col width="10" customWidth="1" min="206" max="206"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1352,6 +1353,9 @@
       <c r="GW1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="GX1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1973,6 +1977,9 @@
       <c r="GW2" t="n">
         <v>-14</v>
       </c>
+      <c r="GX2" t="n">
+        <v>-17</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2593,6 +2600,9 @@
       </c>
       <c r="GW3" t="n">
         <v>-33</v>
+      </c>
+      <c r="GX3" t="n">
+        <v>-37</v>
       </c>
     </row>
   </sheetData>
@@ -2606,7 +2616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IK3"/>
+  <dimension ref="A1:IL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2854,6 +2864,7 @@
     <col width="12" customWidth="1" min="243" max="243"/>
     <col width="12" customWidth="1" min="244" max="244"/>
     <col width="12" customWidth="1" min="245" max="245"/>
+    <col width="12" customWidth="1" min="246" max="246"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4082,6 +4093,11 @@
           <t>20260915</t>
         </is>
       </c>
+      <c r="IL1" s="1" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4763,6 +4779,9 @@
       <c r="IK2" t="n">
         <v>99</v>
       </c>
+      <c r="IL2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5503,6 +5522,9 @@
       </c>
       <c r="IK3" t="n">
         <v>98</v>
+      </c>
+      <c r="IL3" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5516,7 +5538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HR3"/>
+  <dimension ref="A1:HS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5745,6 +5767,7 @@
     <col width="12" customWidth="1" min="224" max="224"/>
     <col width="12" customWidth="1" min="225" max="225"/>
     <col width="12" customWidth="1" min="226" max="226"/>
+    <col width="12" customWidth="1" min="227" max="227"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6878,6 +6901,11 @@
           <t>20260915</t>
         </is>
       </c>
+      <c r="HS1" s="1" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7445,6 +7473,9 @@
       <c r="HR2" t="n">
         <v>-58.13</v>
       </c>
+      <c r="HS2" t="n">
+        <v>-58.58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8128,6 +8159,9 @@
       </c>
       <c r="HR3" t="n">
         <v>-54.61</v>
+      </c>
+      <c r="HS3" t="n">
+        <v>-55.74</v>
       </c>
     </row>
   </sheetData>
@@ -8141,7 +8175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GW3"/>
+  <dimension ref="A1:GX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8349,6 +8383,7 @@
     <col width="12" customWidth="1" min="203" max="203"/>
     <col width="12" customWidth="1" min="204" max="204"/>
     <col width="12" customWidth="1" min="205" max="205"/>
+    <col width="12" customWidth="1" min="206" max="206"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9377,6 +9412,11 @@
           <t>20260915</t>
         </is>
       </c>
+      <c r="GX1" s="1" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9818,6 +9858,9 @@
       <c r="GW2" t="n">
         <v>6</v>
       </c>
+      <c r="GX2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10438,6 +10481,9 @@
       </c>
       <c r="GW3" t="n">
         <v>15</v>
+      </c>
+      <c r="GX3" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -10451,7 +10497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IA3"/>
+  <dimension ref="A1:IB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10689,6 +10735,7 @@
     <col width="10" customWidth="1" min="233" max="233"/>
     <col width="10" customWidth="1" min="234" max="234"/>
     <col width="10" customWidth="1" min="235" max="235"/>
+    <col width="10" customWidth="1" min="236" max="236"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11401,6 +11448,9 @@
       <c r="IA1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="IB1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12112,6 +12162,9 @@
       <c r="IA2" t="n">
         <v>-54</v>
       </c>
+      <c r="IB2" t="n">
+        <v>-59</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12822,6 +12875,9 @@
       </c>
       <c r="IA3" t="n">
         <v>-60</v>
+      </c>
+      <c r="IB3" t="n">
+        <v>-64</v>
       </c>
     </row>
   </sheetData>
@@ -12835,7 +12891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO3"/>
+  <dimension ref="A1:EP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12983,6 +13039,7 @@
     <col width="10" customWidth="1" min="143" max="143"/>
     <col width="10" customWidth="1" min="144" max="144"/>
     <col width="10" customWidth="1" min="145" max="145"/>
+    <col width="10" customWidth="1" min="146" max="146"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13425,6 +13482,9 @@
       <c r="EO1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="EP1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13866,6 +13926,9 @@
       <c r="EO2" t="n">
         <v>80</v>
       </c>
+      <c r="EP2" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14306,6 +14369,9 @@
       </c>
       <c r="EO3" t="n">
         <v>63</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -14319,7 +14385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO3"/>
+  <dimension ref="A1:EP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14467,6 +14533,7 @@
     <col width="10" customWidth="1" min="143" max="143"/>
     <col width="10" customWidth="1" min="144" max="144"/>
     <col width="10" customWidth="1" min="145" max="145"/>
+    <col width="10" customWidth="1" min="146" max="146"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14909,6 +14976,9 @@
       <c r="EO1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="EP1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15350,6 +15420,9 @@
       <c r="EO2" t="n">
         <v>18</v>
       </c>
+      <c r="EP2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15790,6 +15863,9 @@
       </c>
       <c r="EO3" t="n">
         <v>1</v>
+      </c>
+      <c r="EP3" t="n">
+        <v>-2</v>
       </c>
     </row>
   </sheetData>
@@ -15803,7 +15879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GW3"/>
+  <dimension ref="A1:GX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16011,6 +16087,7 @@
     <col width="12" customWidth="1" min="203" max="203"/>
     <col width="12" customWidth="1" min="204" max="204"/>
     <col width="12" customWidth="1" min="205" max="205"/>
+    <col width="12" customWidth="1" min="206" max="206"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17039,6 +17116,11 @@
           <t>20260915</t>
         </is>
       </c>
+      <c r="GX1" s="1" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17480,6 +17562,9 @@
       <c r="GW2" t="n">
         <v>99</v>
       </c>
+      <c r="GX2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18099,6 +18184,9 @@
         <v>95</v>
       </c>
       <c r="GW3" t="n">
+        <v>96</v>
+      </c>
+      <c r="GX3" t="n">
         <v>96</v>
       </c>
     </row>
@@ -18113,7 +18201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IK3"/>
+  <dimension ref="A1:IL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18361,6 +18449,7 @@
     <col width="12" customWidth="1" min="243" max="243"/>
     <col width="12" customWidth="1" min="244" max="244"/>
     <col width="12" customWidth="1" min="245" max="245"/>
+    <col width="12" customWidth="1" min="246" max="246"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19589,6 +19678,11 @@
           <t>20260915</t>
         </is>
       </c>
+      <c r="IL1" s="1" t="inlineStr">
+        <is>
+          <t>20260916</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20270,6 +20364,9 @@
       <c r="IK2" t="n">
         <v>4.83</v>
       </c>
+      <c r="IL2" t="n">
+        <v>4.47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21010,6 +21107,9 @@
       </c>
       <c r="IK3" t="n">
         <v>1.54</v>
+      </c>
+      <c r="IL3" t="n">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>
@@ -21023,7 +21123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JD3"/>
+  <dimension ref="A1:JE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21290,6 +21390,7 @@
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22089,6 +22190,9 @@
       <c r="JD1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="JE1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22884,6 +22988,9 @@
       <c r="JD2" t="n">
         <v>706.25</v>
       </c>
+      <c r="JE2" t="n">
+        <v>706.2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23681,6 +23788,9 @@
       </c>
       <c r="JD3" t="n">
         <v>68.37</v>
+      </c>
+      <c r="JE3" t="n">
+        <v>68.72</v>
       </c>
     </row>
   </sheetData>
@@ -23694,7 +23804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JD3"/>
+  <dimension ref="A1:JE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -23961,6 +24071,7 @@
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24760,6 +24871,9 @@
       <c r="JD1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="JE1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25555,6 +25669,9 @@
       <c r="JD2" t="n">
         <v>712.52</v>
       </c>
+      <c r="JE2" t="n">
+        <v>709.48</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26352,6 +26469,9 @@
       </c>
       <c r="JD3" t="n">
         <v>69.27</v>
+      </c>
+      <c r="JE3" t="n">
+        <v>69.1969</v>
       </c>
     </row>
   </sheetData>
@@ -26365,7 +26485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JD3"/>
+  <dimension ref="A1:JE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26632,6 +26752,7 @@
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27431,6 +27552,9 @@
       <c r="JD1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="JE1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28226,6 +28350,9 @@
       <c r="JD2" t="n">
         <v>703.21</v>
       </c>
+      <c r="JE2" t="n">
+        <v>703.965</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29023,6 +29150,9 @@
       </c>
       <c r="JD3" t="n">
         <v>67.78</v>
+      </c>
+      <c r="JE3" t="n">
+        <v>67.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -29036,7 +29166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JD3"/>
+  <dimension ref="A1:JE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29303,6 +29433,7 @@
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30102,6 +30233,9 @@
       <c r="JD1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="JE1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30897,6 +31031,9 @@
       <c r="JD2" t="n">
         <v>708.98</v>
       </c>
+      <c r="JE2" t="n">
+        <v>707.66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31694,6 +31831,9 @@
       </c>
       <c r="JD3" t="n">
         <v>69.19889999999999</v>
+      </c>
+      <c r="JE3" t="n">
+        <v>68.75</v>
       </c>
     </row>
   </sheetData>
@@ -31707,7 +31847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JD3"/>
+  <dimension ref="A1:JE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -31974,6 +32114,7 @@
     <col width="12" customWidth="1" min="262" max="262"/>
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
+    <col width="12" customWidth="1" min="265" max="265"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32773,6 +32914,9 @@
       <c r="JD1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="JE1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33568,6 +33712,9 @@
       <c r="JD2" t="n">
         <v>353460</v>
       </c>
+      <c r="JE2" t="n">
+        <v>421393</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34365,6 +34512,9 @@
       </c>
       <c r="JD3" t="n">
         <v>1559967</v>
+      </c>
+      <c r="JE3" t="n">
+        <v>1430610</v>
       </c>
     </row>
   </sheetData>
@@ -34378,7 +34528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IK3"/>
+  <dimension ref="A1:IL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34626,6 +34776,7 @@
     <col width="10" customWidth="1" min="243" max="243"/>
     <col width="10" customWidth="1" min="244" max="244"/>
     <col width="10" customWidth="1" min="245" max="245"/>
+    <col width="10" customWidth="1" min="246" max="246"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35368,6 +35519,9 @@
       <c r="IK1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="IL1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36109,6 +36263,9 @@
       <c r="IK2" t="n">
         <v>12</v>
       </c>
+      <c r="IL2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -36849,6 +37006,9 @@
       </c>
       <c r="IK3" t="n">
         <v>9</v>
+      </c>
+      <c r="IL3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -36862,7 +37022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GW3"/>
+  <dimension ref="A1:GX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37070,6 +37230,7 @@
     <col width="10" customWidth="1" min="203" max="203"/>
     <col width="10" customWidth="1" min="204" max="204"/>
     <col width="10" customWidth="1" min="205" max="205"/>
+    <col width="10" customWidth="1" min="206" max="206"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37692,6 +37853,9 @@
       <c r="GW1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="GX1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38313,6 +38477,9 @@
       <c r="GW2" t="n">
         <v>58</v>
       </c>
+      <c r="GX2" t="n">
+        <v>60</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -38933,6 +39100,9 @@
       </c>
       <c r="GW3" t="n">
         <v>42</v>
+      </c>
+      <c r="GX3" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -38946,7 +39116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IK3"/>
+  <dimension ref="A1:IL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39194,6 +39364,7 @@
     <col width="10" customWidth="1" min="243" max="243"/>
     <col width="10" customWidth="1" min="244" max="244"/>
     <col width="10" customWidth="1" min="245" max="245"/>
+    <col width="10" customWidth="1" min="246" max="246"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -39936,6 +40107,9 @@
       <c r="IK1" s="1" t="n">
         <v>20260915</v>
       </c>
+      <c r="IL1" s="1" t="n">
+        <v>20260916</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40677,6 +40851,9 @@
       <c r="IK2" t="n">
         <v>-44</v>
       </c>
+      <c r="IL2" t="n">
+        <v>-54</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41417,6 +41594,9 @@
       </c>
       <c r="IK3" t="n">
         <v>-53</v>
+      </c>
+      <c r="IL3" t="n">
+        <v>-64</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GX3"/>
+  <dimension ref="A1:GY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -731,6 +731,7 @@
     <col width="10" customWidth="1" min="204" max="204"/>
     <col width="10" customWidth="1" min="205" max="205"/>
     <col width="10" customWidth="1" min="206" max="206"/>
+    <col width="10" customWidth="1" min="207" max="207"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1356,6 +1357,9 @@
       <c r="GX1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="GY1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1980,6 +1984,9 @@
       <c r="GX2" t="n">
         <v>-17</v>
       </c>
+      <c r="GY2" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2603,6 +2610,9 @@
       </c>
       <c r="GX3" t="n">
         <v>-37</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>-6</v>
       </c>
     </row>
   </sheetData>
@@ -2616,7 +2626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IL3"/>
+  <dimension ref="A1:IM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2865,6 +2875,7 @@
     <col width="12" customWidth="1" min="244" max="244"/>
     <col width="12" customWidth="1" min="245" max="245"/>
     <col width="12" customWidth="1" min="246" max="246"/>
+    <col width="12" customWidth="1" min="247" max="247"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4098,6 +4109,11 @@
           <t>20260916</t>
         </is>
       </c>
+      <c r="IM1" s="1" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4782,6 +4798,9 @@
       <c r="IL2" t="n">
         <v>99</v>
       </c>
+      <c r="IM2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5525,6 +5544,9 @@
       </c>
       <c r="IL3" t="n">
         <v>97</v>
+      </c>
+      <c r="IM3" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -5538,7 +5560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HS3"/>
+  <dimension ref="A1:HT3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5768,6 +5790,7 @@
     <col width="12" customWidth="1" min="225" max="225"/>
     <col width="12" customWidth="1" min="226" max="226"/>
     <col width="12" customWidth="1" min="227" max="227"/>
+    <col width="12" customWidth="1" min="228" max="228"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6906,6 +6929,11 @@
           <t>20260916</t>
         </is>
       </c>
+      <c r="HT1" s="1" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7476,6 +7504,9 @@
       <c r="HS2" t="n">
         <v>-58.58</v>
       </c>
+      <c r="HT2" t="n">
+        <v>-56.51</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8162,6 +8193,9 @@
       </c>
       <c r="HS3" t="n">
         <v>-55.74</v>
+      </c>
+      <c r="HT3" t="n">
+        <v>-55.21</v>
       </c>
     </row>
   </sheetData>
@@ -8175,7 +8209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GX3"/>
+  <dimension ref="A1:GY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8384,6 +8418,7 @@
     <col width="12" customWidth="1" min="204" max="204"/>
     <col width="12" customWidth="1" min="205" max="205"/>
     <col width="12" customWidth="1" min="206" max="206"/>
+    <col width="12" customWidth="1" min="207" max="207"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9417,6 +9452,11 @@
           <t>20260916</t>
         </is>
       </c>
+      <c r="GY1" s="1" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9861,6 +9901,9 @@
       <c r="GX2" t="n">
         <v>7</v>
       </c>
+      <c r="GY2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10484,6 +10527,9 @@
       </c>
       <c r="GX3" t="n">
         <v>14</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -10497,7 +10543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IB3"/>
+  <dimension ref="A1:IC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10736,6 +10782,7 @@
     <col width="10" customWidth="1" min="234" max="234"/>
     <col width="10" customWidth="1" min="235" max="235"/>
     <col width="10" customWidth="1" min="236" max="236"/>
+    <col width="10" customWidth="1" min="237" max="237"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11451,6 +11498,9 @@
       <c r="IB1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="IC1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12165,6 +12215,9 @@
       <c r="IB2" t="n">
         <v>-59</v>
       </c>
+      <c r="IC2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12878,6 +12931,9 @@
       </c>
       <c r="IB3" t="n">
         <v>-64</v>
+      </c>
+      <c r="IC3" t="n">
+        <v>-14</v>
       </c>
     </row>
   </sheetData>
@@ -12891,7 +12947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP3"/>
+  <dimension ref="A1:EQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13040,6 +13096,7 @@
     <col width="10" customWidth="1" min="144" max="144"/>
     <col width="10" customWidth="1" min="145" max="145"/>
     <col width="10" customWidth="1" min="146" max="146"/>
+    <col width="10" customWidth="1" min="147" max="147"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13485,6 +13542,9 @@
       <c r="EP1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="EQ1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13929,6 +13989,9 @@
       <c r="EP2" t="n">
         <v>79</v>
       </c>
+      <c r="EQ2" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14372,6 +14435,9 @@
       </c>
       <c r="EP3" t="n">
         <v>62</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -14385,7 +14451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP3"/>
+  <dimension ref="A1:EQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14534,6 +14600,7 @@
     <col width="10" customWidth="1" min="144" max="144"/>
     <col width="10" customWidth="1" min="145" max="145"/>
     <col width="10" customWidth="1" min="146" max="146"/>
+    <col width="10" customWidth="1" min="147" max="147"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -14979,6 +15046,9 @@
       <c r="EP1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="EQ1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15423,6 +15493,9 @@
       <c r="EP2" t="n">
         <v>15</v>
       </c>
+      <c r="EQ2" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15866,6 +15939,9 @@
       </c>
       <c r="EP3" t="n">
         <v>-2</v>
+      </c>
+      <c r="EQ3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -15879,7 +15955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GX3"/>
+  <dimension ref="A1:GY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16088,6 +16164,7 @@
     <col width="12" customWidth="1" min="204" max="204"/>
     <col width="12" customWidth="1" min="205" max="205"/>
     <col width="12" customWidth="1" min="206" max="206"/>
+    <col width="12" customWidth="1" min="207" max="207"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17121,6 +17198,11 @@
           <t>20260916</t>
         </is>
       </c>
+      <c r="GY1" s="1" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17565,6 +17647,9 @@
       <c r="GX2" t="n">
         <v>99</v>
       </c>
+      <c r="GY2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18188,6 +18273,9 @@
       </c>
       <c r="GX3" t="n">
         <v>96</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -18201,7 +18289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IL3"/>
+  <dimension ref="A1:IM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18450,6 +18538,7 @@
     <col width="12" customWidth="1" min="244" max="244"/>
     <col width="12" customWidth="1" min="245" max="245"/>
     <col width="12" customWidth="1" min="246" max="246"/>
+    <col width="12" customWidth="1" min="247" max="247"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19683,6 +19772,11 @@
           <t>20260916</t>
         </is>
       </c>
+      <c r="IM1" s="1" t="inlineStr">
+        <is>
+          <t>20260917</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20367,6 +20461,9 @@
       <c r="IL2" t="n">
         <v>4.47</v>
       </c>
+      <c r="IM2" t="n">
+        <v>4.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21110,6 +21207,9 @@
       </c>
       <c r="IL3" t="n">
         <v>1.42</v>
+      </c>
+      <c r="IM3" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>
@@ -21123,7 +21223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JE3"/>
+  <dimension ref="A1:JF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21391,6 +21491,7 @@
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22193,6 +22294,9 @@
       <c r="JE1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="JF1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -22991,6 +23095,9 @@
       <c r="JE2" t="n">
         <v>706.2</v>
       </c>
+      <c r="JF2" t="n">
+        <v>708.4</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23791,6 +23898,9 @@
       </c>
       <c r="JE3" t="n">
         <v>68.72</v>
+      </c>
+      <c r="JF3" t="n">
+        <v>69.73999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -23804,7 +23914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JE3"/>
+  <dimension ref="A1:JF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24072,6 +24182,7 @@
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24874,6 +24985,9 @@
       <c r="JE1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="JF1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25672,6 +25786,9 @@
       <c r="JE2" t="n">
         <v>709.48</v>
       </c>
+      <c r="JF2" t="n">
+        <v>716.76</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26472,6 +26589,9 @@
       </c>
       <c r="JE3" t="n">
         <v>69.1969</v>
+      </c>
+      <c r="JF3" t="n">
+        <v>71.36</v>
       </c>
     </row>
   </sheetData>
@@ -26485,7 +26605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JE3"/>
+  <dimension ref="A1:JF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26753,6 +26873,7 @@
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27555,6 +27676,9 @@
       <c r="JE1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="JF1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28353,6 +28477,9 @@
       <c r="JE2" t="n">
         <v>703.965</v>
       </c>
+      <c r="JF2" t="n">
+        <v>701.6315</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29153,6 +29280,9 @@
       </c>
       <c r="JE3" t="n">
         <v>67.90000000000001</v>
+      </c>
+      <c r="JF3" t="n">
+        <v>68.70999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -29166,7 +29296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JE3"/>
+  <dimension ref="A1:JF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29434,6 +29564,7 @@
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30236,6 +30367,9 @@
       <c r="JE1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="JF1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31034,6 +31168,9 @@
       <c r="JE2" t="n">
         <v>707.66</v>
       </c>
+      <c r="JF2" t="n">
+        <v>716.124</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31834,6 +31971,9 @@
       </c>
       <c r="JE3" t="n">
         <v>68.75</v>
+      </c>
+      <c r="JF3" t="n">
+        <v>71.17</v>
       </c>
     </row>
   </sheetData>
@@ -31847,7 +31987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JE3"/>
+  <dimension ref="A1:JF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32115,6 +32255,7 @@
     <col width="12" customWidth="1" min="263" max="263"/>
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
+    <col width="12" customWidth="1" min="266" max="266"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32917,6 +33058,9 @@
       <c r="JE1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="JF1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33715,6 +33859,9 @@
       <c r="JE2" t="n">
         <v>421393</v>
       </c>
+      <c r="JF2" t="n">
+        <v>602116</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34515,6 +34662,9 @@
       </c>
       <c r="JE3" t="n">
         <v>1430610</v>
+      </c>
+      <c r="JF3" t="n">
+        <v>2063806</v>
       </c>
     </row>
   </sheetData>
@@ -34528,7 +34678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IL3"/>
+  <dimension ref="A1:IM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34777,6 +34927,7 @@
     <col width="10" customWidth="1" min="244" max="244"/>
     <col width="10" customWidth="1" min="245" max="245"/>
     <col width="10" customWidth="1" min="246" max="246"/>
+    <col width="10" customWidth="1" min="247" max="247"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35522,6 +35673,9 @@
       <c r="IL1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="IM1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36266,6 +36420,9 @@
       <c r="IL2" t="n">
         <v>4</v>
       </c>
+      <c r="IM2" t="n">
+        <v>66</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37009,6 +37166,9 @@
       </c>
       <c r="IL3" t="n">
         <v>1</v>
+      </c>
+      <c r="IM3" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -37022,7 +37182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GX3"/>
+  <dimension ref="A1:GY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37231,6 +37391,7 @@
     <col width="10" customWidth="1" min="204" max="204"/>
     <col width="10" customWidth="1" min="205" max="205"/>
     <col width="10" customWidth="1" min="206" max="206"/>
+    <col width="10" customWidth="1" min="207" max="207"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -37856,6 +38017,9 @@
       <c r="GX1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="GY1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38480,6 +38644,9 @@
       <c r="GX2" t="n">
         <v>60</v>
       </c>
+      <c r="GY2" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39103,6 +39270,9 @@
       </c>
       <c r="GX3" t="n">
         <v>51</v>
+      </c>
+      <c r="GY3" t="n">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -39116,7 +39286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IL3"/>
+  <dimension ref="A1:IM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39365,6 +39535,7 @@
     <col width="10" customWidth="1" min="244" max="244"/>
     <col width="10" customWidth="1" min="245" max="245"/>
     <col width="10" customWidth="1" min="246" max="246"/>
+    <col width="10" customWidth="1" min="247" max="247"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40110,6 +40281,9 @@
       <c r="IL1" s="1" t="n">
         <v>20260916</v>
       </c>
+      <c r="IM1" s="1" t="n">
+        <v>20260917</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -40854,6 +41028,9 @@
       <c r="IL2" t="n">
         <v>-54</v>
       </c>
+      <c r="IM2" t="n">
+        <v>41</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41597,6 +41774,9 @@
       </c>
       <c r="IL3" t="n">
         <v>-64</v>
+      </c>
+      <c r="IM3" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GY3"/>
+  <dimension ref="A1:GZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -732,6 +732,7 @@
     <col width="10" customWidth="1" min="205" max="205"/>
     <col width="10" customWidth="1" min="206" max="206"/>
     <col width="10" customWidth="1" min="207" max="207"/>
+    <col width="10" customWidth="1" min="208" max="208"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1360,6 +1361,9 @@
       <c r="GY1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="GZ1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1987,6 +1991,9 @@
       <c r="GY2" t="n">
         <v>15</v>
       </c>
+      <c r="GZ2" t="n">
+        <v>21</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2613,6 +2620,9 @@
       </c>
       <c r="GY3" t="n">
         <v>-6</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2626,7 +2636,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM3"/>
+  <dimension ref="A1:IN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2876,6 +2886,7 @@
     <col width="12" customWidth="1" min="245" max="245"/>
     <col width="12" customWidth="1" min="246" max="246"/>
     <col width="12" customWidth="1" min="247" max="247"/>
+    <col width="12" customWidth="1" min="248" max="248"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4114,6 +4125,11 @@
           <t>20260917</t>
         </is>
       </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4801,6 +4817,9 @@
       <c r="IM2" t="n">
         <v>101</v>
       </c>
+      <c r="IN2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5547,6 +5566,9 @@
       </c>
       <c r="IM3" t="n">
         <v>101</v>
+      </c>
+      <c r="IN3" t="n">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -5560,7 +5582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HT3"/>
+  <dimension ref="A1:HU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5791,6 +5813,7 @@
     <col width="12" customWidth="1" min="226" max="226"/>
     <col width="12" customWidth="1" min="227" max="227"/>
     <col width="12" customWidth="1" min="228" max="228"/>
+    <col width="12" customWidth="1" min="229" max="229"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6934,6 +6957,11 @@
           <t>20260917</t>
         </is>
       </c>
+      <c r="HU1" s="1" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7507,6 +7535,9 @@
       <c r="HT2" t="n">
         <v>-56.51</v>
       </c>
+      <c r="HU2" t="n">
+        <v>-52.82</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8196,6 +8227,9 @@
       </c>
       <c r="HT3" t="n">
         <v>-55.21</v>
+      </c>
+      <c r="HU3" t="n">
+        <v>-53.63</v>
       </c>
     </row>
   </sheetData>
@@ -8209,7 +8243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GY3"/>
+  <dimension ref="A1:GZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8419,6 +8453,7 @@
     <col width="12" customWidth="1" min="205" max="205"/>
     <col width="12" customWidth="1" min="206" max="206"/>
     <col width="12" customWidth="1" min="207" max="207"/>
+    <col width="12" customWidth="1" min="208" max="208"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9457,6 +9492,11 @@
           <t>20260917</t>
         </is>
       </c>
+      <c r="GZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9904,6 +9944,9 @@
       <c r="GY2" t="n">
         <v>10</v>
       </c>
+      <c r="GZ2" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10530,6 +10573,9 @@
       </c>
       <c r="GY3" t="n">
         <v>20</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -10543,7 +10589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IC3"/>
+  <dimension ref="A1:ID3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10783,6 +10829,7 @@
     <col width="10" customWidth="1" min="235" max="235"/>
     <col width="10" customWidth="1" min="236" max="236"/>
     <col width="10" customWidth="1" min="237" max="237"/>
+    <col width="10" customWidth="1" min="238" max="238"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11501,6 +11548,9 @@
       <c r="IC1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="ID1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12218,6 +12268,9 @@
       <c r="IC2" t="n">
         <v>0</v>
       </c>
+      <c r="ID2" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12934,6 +12987,9 @@
       </c>
       <c r="IC3" t="n">
         <v>-14</v>
+      </c>
+      <c r="ID3" t="n">
+        <v>-5</v>
       </c>
     </row>
   </sheetData>
@@ -12947,7 +13003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ3"/>
+  <dimension ref="A1:ER3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13097,6 +13153,7 @@
     <col width="10" customWidth="1" min="145" max="145"/>
     <col width="10" customWidth="1" min="146" max="146"/>
     <col width="10" customWidth="1" min="147" max="147"/>
+    <col width="10" customWidth="1" min="148" max="148"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13545,6 +13602,9 @@
       <c r="EQ1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="ER1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13992,6 +14052,9 @@
       <c r="EQ2" t="n">
         <v>84</v>
       </c>
+      <c r="ER2" t="n">
+        <v>84</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14438,6 +14501,9 @@
       </c>
       <c r="EQ3" t="n">
         <v>67</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -14451,7 +14517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EQ3"/>
+  <dimension ref="A1:ER3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14601,6 +14667,7 @@
     <col width="10" customWidth="1" min="145" max="145"/>
     <col width="10" customWidth="1" min="146" max="146"/>
     <col width="10" customWidth="1" min="147" max="147"/>
+    <col width="10" customWidth="1" min="148" max="148"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15049,6 +15116,9 @@
       <c r="EQ1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="ER1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15496,6 +15566,9 @@
       <c r="EQ2" t="n">
         <v>25</v>
       </c>
+      <c r="ER2" t="n">
+        <v>26</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15942,6 +16015,9 @@
       </c>
       <c r="EQ3" t="n">
         <v>8</v>
+      </c>
+      <c r="ER3" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -15955,7 +16031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GY3"/>
+  <dimension ref="A1:GZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16165,6 +16241,7 @@
     <col width="12" customWidth="1" min="205" max="205"/>
     <col width="12" customWidth="1" min="206" max="206"/>
     <col width="12" customWidth="1" min="207" max="207"/>
+    <col width="12" customWidth="1" min="208" max="208"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17203,6 +17280,11 @@
           <t>20260917</t>
         </is>
       </c>
+      <c r="GZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17650,6 +17732,9 @@
       <c r="GY2" t="n">
         <v>101</v>
       </c>
+      <c r="GZ2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18276,6 +18361,9 @@
       </c>
       <c r="GY3" t="n">
         <v>99</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -18289,7 +18377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM3"/>
+  <dimension ref="A1:IN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18539,6 +18627,7 @@
     <col width="12" customWidth="1" min="245" max="245"/>
     <col width="12" customWidth="1" min="246" max="246"/>
     <col width="12" customWidth="1" min="247" max="247"/>
+    <col width="12" customWidth="1" min="248" max="248"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19777,6 +19866,11 @@
           <t>20260917</t>
         </is>
       </c>
+      <c r="IN1" s="1" t="inlineStr">
+        <is>
+          <t>20260918</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20464,6 +20558,9 @@
       <c r="IM2" t="n">
         <v>4.36</v>
       </c>
+      <c r="IN2" t="n">
+        <v>4.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21210,6 +21307,9 @@
       </c>
       <c r="IM3" t="n">
         <v>1.34</v>
+      </c>
+      <c r="IN3" t="n">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
@@ -21223,7 +21323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JF3"/>
+  <dimension ref="A1:JG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21492,6 +21592,7 @@
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22297,6 +22398,9 @@
       <c r="JF1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="JG1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23098,6 +23202,9 @@
       <c r="JF2" t="n">
         <v>708.4</v>
       </c>
+      <c r="JG2" t="n">
+        <v>721.52</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23901,6 +24008,9 @@
       </c>
       <c r="JF3" t="n">
         <v>69.73999999999999</v>
+      </c>
+      <c r="JG3" t="n">
+        <v>72.72</v>
       </c>
     </row>
   </sheetData>
@@ -23914,7 +24024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JF3"/>
+  <dimension ref="A1:JG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24183,6 +24293,7 @@
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24988,6 +25099,9 @@
       <c r="JF1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="JG1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25789,6 +25903,9 @@
       <c r="JF2" t="n">
         <v>716.76</v>
       </c>
+      <c r="JG2" t="n">
+        <v>722.39</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26592,6 +26709,9 @@
       </c>
       <c r="JF3" t="n">
         <v>71.36</v>
+      </c>
+      <c r="JG3" t="n">
+        <v>72.98</v>
       </c>
     </row>
   </sheetData>
@@ -26605,7 +26725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JF3"/>
+  <dimension ref="A1:JG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26874,6 +26994,7 @@
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27679,6 +27800,9 @@
       <c r="JF1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="JG1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28480,6 +28604,9 @@
       <c r="JF2" t="n">
         <v>701.6315</v>
       </c>
+      <c r="JG2" t="n">
+        <v>715.9773</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29283,6 +29410,9 @@
       </c>
       <c r="JF3" t="n">
         <v>68.70999999999999</v>
+      </c>
+      <c r="JG3" t="n">
+        <v>71.3514</v>
       </c>
     </row>
   </sheetData>
@@ -29296,7 +29426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JF3"/>
+  <dimension ref="A1:JG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29565,6 +29695,7 @@
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30370,6 +30501,9 @@
       <c r="JF1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="JG1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31171,6 +31305,9 @@
       <c r="JF2" t="n">
         <v>716.124</v>
       </c>
+      <c r="JG2" t="n">
+        <v>717.72</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -31974,6 +32111,9 @@
       </c>
       <c r="JF3" t="n">
         <v>71.17</v>
+      </c>
+      <c r="JG3" t="n">
+        <v>71.6185</v>
       </c>
     </row>
   </sheetData>
@@ -31987,7 +32127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JF3"/>
+  <dimension ref="A1:JG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32256,6 +32396,7 @@
     <col width="12" customWidth="1" min="264" max="264"/>
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
+    <col width="12" customWidth="1" min="267" max="267"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33061,6 +33202,9 @@
       <c r="JF1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="JG1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -33862,6 +34006,9 @@
       <c r="JF2" t="n">
         <v>602116</v>
       </c>
+      <c r="JG2" t="n">
+        <v>316631</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34665,6 +34812,9 @@
       </c>
       <c r="JF3" t="n">
         <v>2063806</v>
+      </c>
+      <c r="JG3" t="n">
+        <v>1710924</v>
       </c>
     </row>
   </sheetData>
@@ -34678,7 +34828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM3"/>
+  <dimension ref="A1:IN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -34928,6 +35078,7 @@
     <col width="10" customWidth="1" min="245" max="245"/>
     <col width="10" customWidth="1" min="246" max="246"/>
     <col width="10" customWidth="1" min="247" max="247"/>
+    <col width="10" customWidth="1" min="248" max="248"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35676,6 +35827,9 @@
       <c r="IM1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="IN1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36423,6 +36577,9 @@
       <c r="IM2" t="n">
         <v>66</v>
       </c>
+      <c r="IN2" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37169,6 +37326,9 @@
       </c>
       <c r="IM3" t="n">
         <v>59</v>
+      </c>
+      <c r="IN3" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -37182,7 +37342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GY3"/>
+  <dimension ref="A1:GZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37392,6 +37552,7 @@
     <col width="10" customWidth="1" min="205" max="205"/>
     <col width="10" customWidth="1" min="206" max="206"/>
     <col width="10" customWidth="1" min="207" max="207"/>
+    <col width="10" customWidth="1" min="208" max="208"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38020,6 +38181,9 @@
       <c r="GY1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="GZ1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38647,6 +38811,9 @@
       <c r="GY2" t="n">
         <v>72</v>
       </c>
+      <c r="GZ2" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39273,6 +39440,9 @@
       </c>
       <c r="GY3" t="n">
         <v>64</v>
+      </c>
+      <c r="GZ3" t="n">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -39286,7 +39456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IM3"/>
+  <dimension ref="A1:IN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39536,6 +39706,7 @@
     <col width="10" customWidth="1" min="245" max="245"/>
     <col width="10" customWidth="1" min="246" max="246"/>
     <col width="10" customWidth="1" min="247" max="247"/>
+    <col width="10" customWidth="1" min="248" max="248"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40284,6 +40455,9 @@
       <c r="IM1" s="1" t="n">
         <v>20260917</v>
       </c>
+      <c r="IN1" s="1" t="n">
+        <v>20260918</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41031,6 +41205,9 @@
       <c r="IM2" t="n">
         <v>41</v>
       </c>
+      <c r="IN2" t="n">
+        <v>58</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41777,6 +41954,9 @@
       </c>
       <c r="IM3" t="n">
         <v>23</v>
+      </c>
+      <c r="IN3" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ3"/>
+  <dimension ref="A1:HA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -733,6 +733,7 @@
     <col width="10" customWidth="1" min="206" max="206"/>
     <col width="10" customWidth="1" min="207" max="207"/>
     <col width="10" customWidth="1" min="208" max="208"/>
+    <col width="10" customWidth="1" min="209" max="209"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1364,6 +1365,9 @@
       <c r="GZ1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="HA1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1994,6 +1998,9 @@
       <c r="GZ2" t="n">
         <v>21</v>
       </c>
+      <c r="HA2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2623,6 +2630,9 @@
       </c>
       <c r="GZ3" t="n">
         <v>0</v>
+      </c>
+      <c r="HA3" t="n">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2636,7 +2646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IN3"/>
+  <dimension ref="A1:IO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2887,6 +2897,7 @@
     <col width="12" customWidth="1" min="246" max="246"/>
     <col width="12" customWidth="1" min="247" max="247"/>
     <col width="12" customWidth="1" min="248" max="248"/>
+    <col width="12" customWidth="1" min="249" max="249"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4130,6 +4141,11 @@
           <t>20260918</t>
         </is>
       </c>
+      <c r="IO1" s="1" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4820,6 +4836,9 @@
       <c r="IN2" t="n">
         <v>101</v>
       </c>
+      <c r="IO2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5569,6 +5588,9 @@
       </c>
       <c r="IN3" t="n">
         <v>102</v>
+      </c>
+      <c r="IO3" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -5582,7 +5604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HU3"/>
+  <dimension ref="A1:HV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5814,6 +5836,7 @@
     <col width="12" customWidth="1" min="227" max="227"/>
     <col width="12" customWidth="1" min="228" max="228"/>
     <col width="12" customWidth="1" min="229" max="229"/>
+    <col width="12" customWidth="1" min="230" max="230"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6962,6 +6985,11 @@
           <t>20260918</t>
         </is>
       </c>
+      <c r="HV1" s="1" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7538,6 +7566,9 @@
       <c r="HU2" t="n">
         <v>-52.82</v>
       </c>
+      <c r="HV2" t="n">
+        <v>-26.03</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8230,6 +8261,9 @@
       </c>
       <c r="HU3" t="n">
         <v>-53.63</v>
+      </c>
+      <c r="HV3" t="n">
+        <v>-29.22</v>
       </c>
     </row>
   </sheetData>
@@ -8243,7 +8277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ3"/>
+  <dimension ref="A1:HA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8454,6 +8488,7 @@
     <col width="12" customWidth="1" min="206" max="206"/>
     <col width="12" customWidth="1" min="207" max="207"/>
     <col width="12" customWidth="1" min="208" max="208"/>
+    <col width="12" customWidth="1" min="209" max="209"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9497,6 +9532,11 @@
           <t>20260918</t>
         </is>
       </c>
+      <c r="HA1" s="1" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9947,6 +9987,9 @@
       <c r="GZ2" t="n">
         <v>5</v>
       </c>
+      <c r="HA2" t="n">
+        <v>89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10576,6 +10619,9 @@
       </c>
       <c r="GZ3" t="n">
         <v>16</v>
+      </c>
+      <c r="HA3" t="n">
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -10589,7 +10635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ID3"/>
+  <dimension ref="A1:IE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10830,6 +10876,7 @@
     <col width="10" customWidth="1" min="236" max="236"/>
     <col width="10" customWidth="1" min="237" max="237"/>
     <col width="10" customWidth="1" min="238" max="238"/>
+    <col width="10" customWidth="1" min="239" max="239"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11551,6 +11598,9 @@
       <c r="ID1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="IE1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12271,6 +12321,9 @@
       <c r="ID2" t="n">
         <v>10</v>
       </c>
+      <c r="IE2" t="n">
+        <v>106</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12990,6 +13043,9 @@
       </c>
       <c r="ID3" t="n">
         <v>-5</v>
+      </c>
+      <c r="IE3" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -13003,7 +13059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ER3"/>
+  <dimension ref="A1:ES3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13154,6 +13210,7 @@
     <col width="10" customWidth="1" min="146" max="146"/>
     <col width="10" customWidth="1" min="147" max="147"/>
     <col width="10" customWidth="1" min="148" max="148"/>
+    <col width="10" customWidth="1" min="149" max="149"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13605,6 +13662,9 @@
       <c r="ER1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="ES1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14055,6 +14115,9 @@
       <c r="ER2" t="n">
         <v>84</v>
       </c>
+      <c r="ES2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14504,6 +14567,9 @@
       </c>
       <c r="ER3" t="n">
         <v>68</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -14517,7 +14583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ER3"/>
+  <dimension ref="A1:ES3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14668,6 +14734,7 @@
     <col width="10" customWidth="1" min="146" max="146"/>
     <col width="10" customWidth="1" min="147" max="147"/>
     <col width="10" customWidth="1" min="148" max="148"/>
+    <col width="10" customWidth="1" min="149" max="149"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15119,6 +15186,9 @@
       <c r="ER1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="ES1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15569,6 +15639,9 @@
       <c r="ER2" t="n">
         <v>26</v>
       </c>
+      <c r="ES2" t="n">
+        <v>46</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16018,6 +16091,9 @@
       </c>
       <c r="ER3" t="n">
         <v>9</v>
+      </c>
+      <c r="ES3" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -16031,7 +16107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ3"/>
+  <dimension ref="A1:HA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16242,6 +16318,7 @@
     <col width="12" customWidth="1" min="206" max="206"/>
     <col width="12" customWidth="1" min="207" max="207"/>
     <col width="12" customWidth="1" min="208" max="208"/>
+    <col width="12" customWidth="1" min="209" max="209"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17285,6 +17362,11 @@
           <t>20260918</t>
         </is>
       </c>
+      <c r="HA1" s="1" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17735,6 +17817,9 @@
       <c r="GZ2" t="n">
         <v>101</v>
       </c>
+      <c r="HA2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18364,6 +18449,9 @@
       </c>
       <c r="GZ3" t="n">
         <v>100</v>
+      </c>
+      <c r="HA3" t="n">
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -18377,7 +18465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IN3"/>
+  <dimension ref="A1:IO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18628,6 +18716,7 @@
     <col width="12" customWidth="1" min="246" max="246"/>
     <col width="12" customWidth="1" min="247" max="247"/>
     <col width="12" customWidth="1" min="248" max="248"/>
+    <col width="12" customWidth="1" min="249" max="249"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19871,6 +19960,11 @@
           <t>20260918</t>
         </is>
       </c>
+      <c r="IO1" s="1" t="inlineStr">
+        <is>
+          <t>20260921</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20561,6 +20655,9 @@
       <c r="IN2" t="n">
         <v>4.36</v>
       </c>
+      <c r="IO2" t="n">
+        <v>6.36</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21310,6 +21407,9 @@
       </c>
       <c r="IN3" t="n">
         <v>1.29</v>
+      </c>
+      <c r="IO3" t="n">
+        <v>1.85</v>
       </c>
     </row>
   </sheetData>
@@ -21323,7 +21423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JG3"/>
+  <dimension ref="A1:JH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21593,6 +21693,7 @@
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22401,6 +22502,9 @@
       <c r="JG1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="JH1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23205,6 +23309,9 @@
       <c r="JG2" t="n">
         <v>721.52</v>
       </c>
+      <c r="JH2" t="n">
+        <v>727.95</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24011,6 +24118,9 @@
       </c>
       <c r="JG3" t="n">
         <v>72.72</v>
+      </c>
+      <c r="JH3" t="n">
+        <v>74.845</v>
       </c>
     </row>
   </sheetData>
@@ -24024,7 +24134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JG3"/>
+  <dimension ref="A1:JH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24294,6 +24404,7 @@
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25102,6 +25213,9 @@
       <c r="JG1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="JH1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -25906,6 +26020,9 @@
       <c r="JG2" t="n">
         <v>722.39</v>
       </c>
+      <c r="JH2" t="n">
+        <v>733.8099999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26712,6 +26829,9 @@
       </c>
       <c r="JG3" t="n">
         <v>72.98</v>
+      </c>
+      <c r="JH3" t="n">
+        <v>76.65000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -26725,7 +26845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JG3"/>
+  <dimension ref="A1:JH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -26995,6 +27115,7 @@
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27803,6 +27924,9 @@
       <c r="JG1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="JH1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28607,6 +28731,9 @@
       <c r="JG2" t="n">
         <v>715.9773</v>
       </c>
+      <c r="JH2" t="n">
+        <v>727.8200000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29413,6 +29540,9 @@
       </c>
       <c r="JG3" t="n">
         <v>71.3514</v>
+      </c>
+      <c r="JH3" t="n">
+        <v>74.84</v>
       </c>
     </row>
   </sheetData>
@@ -29426,7 +29556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JG3"/>
+  <dimension ref="A1:JH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29696,6 +29826,7 @@
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30504,6 +30635,9 @@
       <c r="JG1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="JH1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31308,6 +31442,9 @@
       <c r="JG2" t="n">
         <v>717.72</v>
       </c>
+      <c r="JH2" t="n">
+        <v>733.73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32114,6 +32251,9 @@
       </c>
       <c r="JG3" t="n">
         <v>71.6185</v>
+      </c>
+      <c r="JH3" t="n">
+        <v>76.62</v>
       </c>
     </row>
   </sheetData>
@@ -32127,7 +32267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JG3"/>
+  <dimension ref="A1:JH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32397,6 +32537,7 @@
     <col width="12" customWidth="1" min="265" max="265"/>
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
+    <col width="12" customWidth="1" min="268" max="268"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33205,6 +33346,9 @@
       <c r="JG1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="JH1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34009,6 +34153,9 @@
       <c r="JG2" t="n">
         <v>316631</v>
       </c>
+      <c r="JH2" t="n">
+        <v>5527118</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34815,6 +34962,9 @@
       </c>
       <c r="JG3" t="n">
         <v>1710924</v>
+      </c>
+      <c r="JH3" t="n">
+        <v>11239210</v>
       </c>
     </row>
   </sheetData>
@@ -34828,7 +34978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IN3"/>
+  <dimension ref="A1:IO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35079,6 +35229,7 @@
     <col width="10" customWidth="1" min="246" max="246"/>
     <col width="10" customWidth="1" min="247" max="247"/>
     <col width="10" customWidth="1" min="248" max="248"/>
+    <col width="10" customWidth="1" min="249" max="249"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35830,6 +35981,9 @@
       <c r="IN1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="IO1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36580,6 +36734,9 @@
       <c r="IN2" t="n">
         <v>78</v>
       </c>
+      <c r="IO2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37329,6 +37486,9 @@
       </c>
       <c r="IN3" t="n">
         <v>70</v>
+      </c>
+      <c r="IO3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -37342,7 +37502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:GZ3"/>
+  <dimension ref="A1:HA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37553,6 +37713,7 @@
     <col width="10" customWidth="1" min="206" max="206"/>
     <col width="10" customWidth="1" min="207" max="207"/>
     <col width="10" customWidth="1" min="208" max="208"/>
+    <col width="10" customWidth="1" min="209" max="209"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38184,6 +38345,9 @@
       <c r="GZ1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="HA1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38814,6 +38978,9 @@
       <c r="GZ2" t="n">
         <v>75</v>
       </c>
+      <c r="HA2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39443,6 +39610,9 @@
       </c>
       <c r="GZ3" t="n">
         <v>66</v>
+      </c>
+      <c r="HA3" t="n">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -39456,7 +39626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IN3"/>
+  <dimension ref="A1:IO3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39707,6 +39877,7 @@
     <col width="10" customWidth="1" min="246" max="246"/>
     <col width="10" customWidth="1" min="247" max="247"/>
     <col width="10" customWidth="1" min="248" max="248"/>
+    <col width="10" customWidth="1" min="249" max="249"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40458,6 +40629,9 @@
       <c r="IN1" s="1" t="n">
         <v>20260918</v>
       </c>
+      <c r="IO1" s="1" t="n">
+        <v>20260921</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41208,6 +41382,9 @@
       <c r="IN2" t="n">
         <v>58</v>
       </c>
+      <c r="IO2" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -41957,6 +42134,9 @@
       </c>
       <c r="IN3" t="n">
         <v>42</v>
+      </c>
+      <c r="IO3" t="n">
+        <v>155</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HA3"/>
+  <dimension ref="A1:HB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -734,6 +734,7 @@
     <col width="10" customWidth="1" min="207" max="207"/>
     <col width="10" customWidth="1" min="208" max="208"/>
     <col width="10" customWidth="1" min="209" max="209"/>
+    <col width="10" customWidth="1" min="210" max="210"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1368,6 +1369,9 @@
       <c r="HA1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="HB1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2001,6 +2005,9 @@
       <c r="HA2" t="n">
         <v>80</v>
       </c>
+      <c r="HB2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2633,6 +2640,9 @@
       </c>
       <c r="HA3" t="n">
         <v>63</v>
+      </c>
+      <c r="HB3" t="n">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -2646,7 +2656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IO3"/>
+  <dimension ref="A1:IP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2898,6 +2908,7 @@
     <col width="12" customWidth="1" min="247" max="247"/>
     <col width="12" customWidth="1" min="248" max="248"/>
     <col width="12" customWidth="1" min="249" max="249"/>
+    <col width="12" customWidth="1" min="250" max="250"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4146,6 +4157,11 @@
           <t>20260921</t>
         </is>
       </c>
+      <c r="IP1" s="1" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4839,6 +4855,9 @@
       <c r="IO2" t="n">
         <v>103</v>
       </c>
+      <c r="IP2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5591,6 +5610,9 @@
       </c>
       <c r="IO3" t="n">
         <v>108</v>
+      </c>
+      <c r="IP3" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -5604,7 +5626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HV3"/>
+  <dimension ref="A1:HW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5837,6 +5859,7 @@
     <col width="12" customWidth="1" min="228" max="228"/>
     <col width="12" customWidth="1" min="229" max="229"/>
     <col width="12" customWidth="1" min="230" max="230"/>
+    <col width="12" customWidth="1" min="231" max="231"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6990,6 +7013,11 @@
           <t>20260921</t>
         </is>
       </c>
+      <c r="HW1" s="1" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7569,6 +7597,9 @@
       <c r="HV2" t="n">
         <v>-26.03</v>
       </c>
+      <c r="HW2" t="n">
+        <v>7.24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8264,6 +8295,9 @@
       </c>
       <c r="HV3" t="n">
         <v>-29.22</v>
+      </c>
+      <c r="HW3" t="n">
+        <v>2.51</v>
       </c>
     </row>
   </sheetData>
@@ -8277,7 +8311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HA3"/>
+  <dimension ref="A1:HB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8489,6 +8523,7 @@
     <col width="12" customWidth="1" min="207" max="207"/>
     <col width="12" customWidth="1" min="208" max="208"/>
     <col width="12" customWidth="1" min="209" max="209"/>
+    <col width="12" customWidth="1" min="210" max="210"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9537,6 +9572,11 @@
           <t>20260921</t>
         </is>
       </c>
+      <c r="HB1" s="1" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9990,6 +10030,9 @@
       <c r="HA2" t="n">
         <v>89</v>
       </c>
+      <c r="HB2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10622,6 +10665,9 @@
       </c>
       <c r="HA3" t="n">
         <v>104</v>
+      </c>
+      <c r="HB3" t="n">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -10635,7 +10681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IE3"/>
+  <dimension ref="A1:IF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10877,6 +10923,7 @@
     <col width="10" customWidth="1" min="237" max="237"/>
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
+    <col width="10" customWidth="1" min="240" max="240"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11601,6 +11648,9 @@
       <c r="IE1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="IF1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12324,6 +12374,9 @@
       <c r="IE2" t="n">
         <v>106</v>
       </c>
+      <c r="IF2" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13046,6 +13099,9 @@
       </c>
       <c r="IE3" t="n">
         <v>89</v>
+      </c>
+      <c r="IF3" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -13059,7 +13115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ES3"/>
+  <dimension ref="A1:ET3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13211,6 +13267,7 @@
     <col width="10" customWidth="1" min="147" max="147"/>
     <col width="10" customWidth="1" min="148" max="148"/>
     <col width="10" customWidth="1" min="149" max="149"/>
+    <col width="10" customWidth="1" min="150" max="150"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13665,6 +13722,9 @@
       <c r="ES1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="ET1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14118,6 +14178,9 @@
       <c r="ES2" t="n">
         <v>92</v>
       </c>
+      <c r="ET2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14570,6 +14633,9 @@
       </c>
       <c r="ES3" t="n">
         <v>76</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -14583,7 +14649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ES3"/>
+  <dimension ref="A1:ET3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14735,6 +14801,7 @@
     <col width="10" customWidth="1" min="147" max="147"/>
     <col width="10" customWidth="1" min="148" max="148"/>
     <col width="10" customWidth="1" min="149" max="149"/>
+    <col width="10" customWidth="1" min="150" max="150"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15189,6 +15256,9 @@
       <c r="ES1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="ET1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15642,6 +15712,9 @@
       <c r="ES2" t="n">
         <v>46</v>
       </c>
+      <c r="ET2" t="n">
+        <v>56</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16094,6 +16167,9 @@
       </c>
       <c r="ES3" t="n">
         <v>34</v>
+      </c>
+      <c r="ET3" t="n">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -16107,7 +16183,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HA3"/>
+  <dimension ref="A1:HB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16319,6 +16395,7 @@
     <col width="12" customWidth="1" min="207" max="207"/>
     <col width="12" customWidth="1" min="208" max="208"/>
     <col width="12" customWidth="1" min="209" max="209"/>
+    <col width="12" customWidth="1" min="210" max="210"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17367,6 +17444,11 @@
           <t>20260921</t>
         </is>
       </c>
+      <c r="HB1" s="1" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17820,6 +17902,9 @@
       <c r="HA2" t="n">
         <v>103</v>
       </c>
+      <c r="HB2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18452,6 +18537,9 @@
       </c>
       <c r="HA3" t="n">
         <v>107</v>
+      </c>
+      <c r="HB3" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -18465,7 +18553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IO3"/>
+  <dimension ref="A1:IP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18717,6 +18805,7 @@
     <col width="12" customWidth="1" min="247" max="247"/>
     <col width="12" customWidth="1" min="248" max="248"/>
     <col width="12" customWidth="1" min="249" max="249"/>
+    <col width="12" customWidth="1" min="250" max="250"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19965,6 +20054,11 @@
           <t>20260921</t>
         </is>
       </c>
+      <c r="IP1" s="1" t="inlineStr">
+        <is>
+          <t>20260922</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20658,6 +20752,9 @@
       <c r="IO2" t="n">
         <v>6.36</v>
       </c>
+      <c r="IP2" t="n">
+        <v>8.65</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21410,6 +21507,9 @@
       </c>
       <c r="IO3" t="n">
         <v>1.85</v>
+      </c>
+      <c r="IP3" t="n">
+        <v>2.54</v>
       </c>
     </row>
   </sheetData>
@@ -21423,7 +21523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JH3"/>
+  <dimension ref="A1:JI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21694,6 +21794,7 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22505,6 +22606,9 @@
       <c r="JH1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="JI1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23312,6 +23416,9 @@
       <c r="JH2" t="n">
         <v>727.95</v>
       </c>
+      <c r="JI2" t="n">
+        <v>741.13</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24121,6 +24228,9 @@
       </c>
       <c r="JH3" t="n">
         <v>74.845</v>
+      </c>
+      <c r="JI3" t="n">
+        <v>78.83</v>
       </c>
     </row>
   </sheetData>
@@ -24134,7 +24244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JH3"/>
+  <dimension ref="A1:JI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24405,6 +24515,7 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25216,6 +25327,9 @@
       <c r="JH1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="JI1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26023,6 +26137,9 @@
       <c r="JH2" t="n">
         <v>733.8099999999999</v>
       </c>
+      <c r="JI2" t="n">
+        <v>743.6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26832,6 +26949,9 @@
       </c>
       <c r="JH3" t="n">
         <v>76.65000000000001</v>
+      </c>
+      <c r="JI3" t="n">
+        <v>79.61</v>
       </c>
     </row>
   </sheetData>
@@ -26845,7 +26965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JH3"/>
+  <dimension ref="A1:JI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27116,6 +27236,7 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -27927,6 +28048,9 @@
       <c r="JH1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="JI1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28734,6 +28858,9 @@
       <c r="JH2" t="n">
         <v>727.8200000000001</v>
       </c>
+      <c r="JI2" t="n">
+        <v>738.6799999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29543,6 +29670,9 @@
       </c>
       <c r="JH3" t="n">
         <v>74.84</v>
+      </c>
+      <c r="JI3" t="n">
+        <v>78.05</v>
       </c>
     </row>
   </sheetData>
@@ -29556,7 +29686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JH3"/>
+  <dimension ref="A1:JI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29827,6 +29957,7 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30638,6 +30769,9 @@
       <c r="JH1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="JI1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31445,6 +31579,9 @@
       <c r="JH2" t="n">
         <v>733.73</v>
       </c>
+      <c r="JI2" t="n">
+        <v>741.2243</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32254,6 +32391,9 @@
       </c>
       <c r="JH3" t="n">
         <v>76.62</v>
+      </c>
+      <c r="JI3" t="n">
+        <v>78.87949999999999</v>
       </c>
     </row>
   </sheetData>
@@ -32267,7 +32407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JH3"/>
+  <dimension ref="A1:JI3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32538,6 +32678,7 @@
     <col width="12" customWidth="1" min="266" max="266"/>
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
+    <col width="12" customWidth="1" min="269" max="269"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33349,6 +33490,9 @@
       <c r="JH1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="JI1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34156,6 +34300,9 @@
       <c r="JH2" t="n">
         <v>5527118</v>
       </c>
+      <c r="JI2" t="n">
+        <v>422643</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -34965,6 +35112,9 @@
       </c>
       <c r="JH3" t="n">
         <v>11239210</v>
+      </c>
+      <c r="JI3" t="n">
+        <v>1805521</v>
       </c>
     </row>
   </sheetData>
@@ -34978,7 +35128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IO3"/>
+  <dimension ref="A1:IP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35230,6 +35380,7 @@
     <col width="10" customWidth="1" min="247" max="247"/>
     <col width="10" customWidth="1" min="248" max="248"/>
     <col width="10" customWidth="1" min="249" max="249"/>
+    <col width="10" customWidth="1" min="250" max="250"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -35984,6 +36135,9 @@
       <c r="IO1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="IP1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36737,6 +36891,9 @@
       <c r="IO2" t="n">
         <v>100</v>
       </c>
+      <c r="IP2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37488,6 +37645,9 @@
         <v>70</v>
       </c>
       <c r="IO3" t="n">
+        <v>100</v>
+      </c>
+      <c r="IP3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -37502,7 +37662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HA3"/>
+  <dimension ref="A1:HB3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37714,6 +37874,7 @@
     <col width="10" customWidth="1" min="207" max="207"/>
     <col width="10" customWidth="1" min="208" max="208"/>
     <col width="10" customWidth="1" min="209" max="209"/>
+    <col width="10" customWidth="1" min="210" max="210"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38348,6 +38509,9 @@
       <c r="HA1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="HB1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -38981,6 +39145,9 @@
       <c r="HA2" t="n">
         <v>98</v>
       </c>
+      <c r="HB2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39613,6 +39780,9 @@
       </c>
       <c r="HA3" t="n">
         <v>93</v>
+      </c>
+      <c r="HB3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -39626,7 +39796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IO3"/>
+  <dimension ref="A1:IP3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -39878,6 +40048,7 @@
     <col width="10" customWidth="1" min="247" max="247"/>
     <col width="10" customWidth="1" min="248" max="248"/>
     <col width="10" customWidth="1" min="249" max="249"/>
+    <col width="10" customWidth="1" min="250" max="250"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40632,6 +40803,9 @@
       <c r="IO1" s="1" t="n">
         <v>20260921</v>
       </c>
+      <c r="IP1" s="1" t="n">
+        <v>20260922</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41385,6 +41559,9 @@
       <c r="IO2" t="n">
         <v>156</v>
       </c>
+      <c r="IP2" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42137,6 +42314,9 @@
       </c>
       <c r="IO3" t="n">
         <v>155</v>
+      </c>
+      <c r="IP3" t="n">
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HB3"/>
+  <dimension ref="A1:HC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -735,6 +735,7 @@
     <col width="10" customWidth="1" min="208" max="208"/>
     <col width="10" customWidth="1" min="209" max="209"/>
     <col width="10" customWidth="1" min="210" max="210"/>
+    <col width="10" customWidth="1" min="211" max="211"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1372,6 +1373,9 @@
       <c r="HB1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="HC1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2008,6 +2012,9 @@
       <c r="HB2" t="n">
         <v>103</v>
       </c>
+      <c r="HC2" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2643,6 +2650,9 @@
       </c>
       <c r="HB3" t="n">
         <v>88</v>
+      </c>
+      <c r="HC3" t="n">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2656,7 +2666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IP3"/>
+  <dimension ref="A1:IQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2909,6 +2919,7 @@
     <col width="12" customWidth="1" min="248" max="248"/>
     <col width="12" customWidth="1" min="249" max="249"/>
     <col width="12" customWidth="1" min="250" max="250"/>
+    <col width="12" customWidth="1" min="251" max="251"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4162,6 +4173,11 @@
           <t>20260922</t>
         </is>
       </c>
+      <c r="IQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4858,6 +4874,9 @@
       <c r="IP2" t="n">
         <v>104</v>
       </c>
+      <c r="IQ2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5613,6 +5632,9 @@
       </c>
       <c r="IP3" t="n">
         <v>111</v>
+      </c>
+      <c r="IQ3" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -5626,7 +5648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HW3"/>
+  <dimension ref="A1:HX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5860,6 +5882,7 @@
     <col width="12" customWidth="1" min="229" max="229"/>
     <col width="12" customWidth="1" min="230" max="230"/>
     <col width="12" customWidth="1" min="231" max="231"/>
+    <col width="12" customWidth="1" min="232" max="232"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7018,6 +7041,11 @@
           <t>20260922</t>
         </is>
       </c>
+      <c r="HX1" s="1" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7600,6 +7628,9 @@
       <c r="HW2" t="n">
         <v>7.24</v>
       </c>
+      <c r="HX2" t="n">
+        <v>39.63</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8298,6 +8329,9 @@
       </c>
       <c r="HW3" t="n">
         <v>2.51</v>
+      </c>
+      <c r="HX3" t="n">
+        <v>32.49</v>
       </c>
     </row>
   </sheetData>
@@ -8311,7 +8345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HB3"/>
+  <dimension ref="A1:HC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8524,6 +8558,7 @@
     <col width="12" customWidth="1" min="208" max="208"/>
     <col width="12" customWidth="1" min="209" max="209"/>
     <col width="12" customWidth="1" min="210" max="210"/>
+    <col width="12" customWidth="1" min="211" max="211"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9577,6 +9612,11 @@
           <t>20260922</t>
         </is>
       </c>
+      <c r="HC1" s="1" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10033,6 +10073,9 @@
       <c r="HB2" t="n">
         <v>7</v>
       </c>
+      <c r="HC2" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10668,6 +10711,9 @@
       </c>
       <c r="HB3" t="n">
         <v>17</v>
+      </c>
+      <c r="HC3" t="n">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -10681,7 +10727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IF3"/>
+  <dimension ref="A1:IG3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10924,6 +10970,7 @@
     <col width="10" customWidth="1" min="238" max="238"/>
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
+    <col width="10" customWidth="1" min="241" max="241"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11651,6 +11698,9 @@
       <c r="IF1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="IG1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12377,6 +12427,9 @@
       <c r="IF2" t="n">
         <v>133</v>
       </c>
+      <c r="IG2" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13102,6 +13155,9 @@
       </c>
       <c r="IF3" t="n">
         <v>120</v>
+      </c>
+      <c r="IG3" t="n">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -13115,7 +13171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET3"/>
+  <dimension ref="A1:EU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13268,6 +13324,7 @@
     <col width="10" customWidth="1" min="148" max="148"/>
     <col width="10" customWidth="1" min="149" max="149"/>
     <col width="10" customWidth="1" min="150" max="150"/>
+    <col width="10" customWidth="1" min="151" max="151"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13725,6 +13782,9 @@
       <c r="ET1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="EU1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14181,6 +14241,9 @@
       <c r="ET2" t="n">
         <v>96</v>
       </c>
+      <c r="EU2" t="n">
+        <v>99</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14636,6 +14699,9 @@
       </c>
       <c r="ET3" t="n">
         <v>80</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -14649,7 +14715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:ET3"/>
+  <dimension ref="A1:EU3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14802,6 +14868,7 @@
     <col width="10" customWidth="1" min="148" max="148"/>
     <col width="10" customWidth="1" min="149" max="149"/>
     <col width="10" customWidth="1" min="150" max="150"/>
+    <col width="10" customWidth="1" min="151" max="151"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15259,6 +15326,9 @@
       <c r="ET1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="EU1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15715,6 +15785,9 @@
       <c r="ET2" t="n">
         <v>56</v>
       </c>
+      <c r="EU2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16170,6 +16243,9 @@
       </c>
       <c r="ET3" t="n">
         <v>45</v>
+      </c>
+      <c r="EU3" t="n">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -16183,7 +16259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HB3"/>
+  <dimension ref="A1:HC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16396,6 +16472,7 @@
     <col width="12" customWidth="1" min="208" max="208"/>
     <col width="12" customWidth="1" min="209" max="209"/>
     <col width="12" customWidth="1" min="210" max="210"/>
+    <col width="12" customWidth="1" min="211" max="211"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17449,6 +17526,11 @@
           <t>20260922</t>
         </is>
       </c>
+      <c r="HC1" s="1" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17905,6 +17987,9 @@
       <c r="HB2" t="n">
         <v>104</v>
       </c>
+      <c r="HC2" t="n">
+        <v>105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18540,6 +18625,9 @@
       </c>
       <c r="HB3" t="n">
         <v>110</v>
+      </c>
+      <c r="HC3" t="n">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
@@ -18553,7 +18641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IP3"/>
+  <dimension ref="A1:IQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18806,6 +18894,7 @@
     <col width="12" customWidth="1" min="248" max="248"/>
     <col width="12" customWidth="1" min="249" max="249"/>
     <col width="12" customWidth="1" min="250" max="250"/>
+    <col width="12" customWidth="1" min="251" max="251"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20059,6 +20148,11 @@
           <t>20260922</t>
         </is>
       </c>
+      <c r="IQ1" s="1" t="inlineStr">
+        <is>
+          <t>20260923</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20755,6 +20849,9 @@
       <c r="IP2" t="n">
         <v>8.65</v>
       </c>
+      <c r="IQ2" t="n">
+        <v>10.8</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21510,6 +21607,9 @@
       </c>
       <c r="IP3" t="n">
         <v>2.54</v>
+      </c>
+      <c r="IQ3" t="n">
+        <v>3.17</v>
       </c>
     </row>
   </sheetData>
@@ -21523,7 +21623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JI3"/>
+  <dimension ref="A1:JJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21795,6 +21895,7 @@
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22609,6 +22710,9 @@
       <c r="JI1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="JJ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23419,6 +23523,9 @@
       <c r="JI2" t="n">
         <v>741.13</v>
       </c>
+      <c r="JJ2" t="n">
+        <v>747.6212</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24231,6 +24338,9 @@
       </c>
       <c r="JI3" t="n">
         <v>78.83</v>
+      </c>
+      <c r="JJ3" t="n">
+        <v>80.73999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -24244,7 +24354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JI3"/>
+  <dimension ref="A1:JJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24516,6 +24626,7 @@
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25330,6 +25441,9 @@
       <c r="JI1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="JJ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26140,6 +26254,9 @@
       <c r="JI2" t="n">
         <v>743.6</v>
       </c>
+      <c r="JJ2" t="n">
+        <v>749.08</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -26952,6 +27069,9 @@
       </c>
       <c r="JI3" t="n">
         <v>79.61</v>
+      </c>
+      <c r="JJ3" t="n">
+        <v>81.2</v>
       </c>
     </row>
   </sheetData>
@@ -26965,7 +27085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JI3"/>
+  <dimension ref="A1:JJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27237,6 +27357,7 @@
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28051,6 +28172,9 @@
       <c r="JI1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="JJ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28861,6 +28985,9 @@
       <c r="JI2" t="n">
         <v>738.6799999999999</v>
       </c>
+      <c r="JJ2" t="n">
+        <v>744.688</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29673,6 +29800,9 @@
       </c>
       <c r="JI3" t="n">
         <v>78.05</v>
+      </c>
+      <c r="JJ3" t="n">
+        <v>79.78</v>
       </c>
     </row>
   </sheetData>
@@ -29686,7 +29816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JI3"/>
+  <dimension ref="A1:JJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -29958,6 +30088,7 @@
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30772,6 +30903,9 @@
       <c r="JI1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="JJ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31582,6 +31716,9 @@
       <c r="JI2" t="n">
         <v>741.2243</v>
       </c>
+      <c r="JJ2" t="n">
+        <v>745.6993</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32394,6 +32531,9 @@
       </c>
       <c r="JI3" t="n">
         <v>78.87949999999999</v>
+      </c>
+      <c r="JJ3" t="n">
+        <v>80.11</v>
       </c>
     </row>
   </sheetData>
@@ -32407,7 +32547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JI3"/>
+  <dimension ref="A1:JJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32679,6 +32819,7 @@
     <col width="12" customWidth="1" min="267" max="267"/>
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
+    <col width="12" customWidth="1" min="270" max="270"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33493,6 +33634,9 @@
       <c r="JI1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="JJ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34303,6 +34447,9 @@
       <c r="JI2" t="n">
         <v>422643</v>
       </c>
+      <c r="JJ2" t="n">
+        <v>355336</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35115,6 +35262,9 @@
       </c>
       <c r="JI3" t="n">
         <v>1805521</v>
+      </c>
+      <c r="JJ3" t="n">
+        <v>1789031</v>
       </c>
     </row>
   </sheetData>
@@ -35128,7 +35278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IP3"/>
+  <dimension ref="A1:IQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35381,6 +35531,7 @@
     <col width="10" customWidth="1" min="248" max="248"/>
     <col width="10" customWidth="1" min="249" max="249"/>
     <col width="10" customWidth="1" min="250" max="250"/>
+    <col width="10" customWidth="1" min="251" max="251"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36138,6 +36289,9 @@
       <c r="IP1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="IQ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -36894,6 +37048,9 @@
       <c r="IP2" t="n">
         <v>100</v>
       </c>
+      <c r="IQ2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37648,6 +37805,9 @@
         <v>100</v>
       </c>
       <c r="IP3" t="n">
+        <v>100</v>
+      </c>
+      <c r="IQ3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -37662,7 +37822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HB3"/>
+  <dimension ref="A1:HC3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -37875,6 +38035,7 @@
     <col width="10" customWidth="1" min="208" max="208"/>
     <col width="10" customWidth="1" min="209" max="209"/>
     <col width="10" customWidth="1" min="210" max="210"/>
+    <col width="10" customWidth="1" min="211" max="211"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38512,6 +38673,9 @@
       <c r="HB1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="HC1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39148,6 +39312,9 @@
       <c r="HB2" t="n">
         <v>100</v>
       </c>
+      <c r="HC2" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39782,6 +39949,9 @@
         <v>93</v>
       </c>
       <c r="HB3" t="n">
+        <v>100</v>
+      </c>
+      <c r="HC3" t="n">
         <v>100</v>
       </c>
     </row>
@@ -39796,7 +39966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IP3"/>
+  <dimension ref="A1:IQ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40049,6 +40219,7 @@
     <col width="10" customWidth="1" min="248" max="248"/>
     <col width="10" customWidth="1" min="249" max="249"/>
     <col width="10" customWidth="1" min="250" max="250"/>
+    <col width="10" customWidth="1" min="251" max="251"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40806,6 +40977,9 @@
       <c r="IP1" s="1" t="n">
         <v>20260922</v>
       </c>
+      <c r="IQ1" s="1" t="n">
+        <v>20260923</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41562,6 +41736,9 @@
       <c r="IP2" t="n">
         <v>147</v>
       </c>
+      <c r="IQ2" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42317,6 +42494,9 @@
       </c>
       <c r="IP3" t="n">
         <v>147</v>
+      </c>
+      <c r="IQ3" t="n">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HC3"/>
+  <dimension ref="A1:HD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -736,6 +736,7 @@
     <col width="10" customWidth="1" min="209" max="209"/>
     <col width="10" customWidth="1" min="210" max="210"/>
     <col width="10" customWidth="1" min="211" max="211"/>
+    <col width="10" customWidth="1" min="212" max="212"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1376,6 +1377,9 @@
       <c r="HC1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="HD1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2015,6 +2019,9 @@
       <c r="HC2" t="n">
         <v>112</v>
       </c>
+      <c r="HD2" t="n">
+        <v>71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2653,6 +2660,9 @@
       </c>
       <c r="HC3" t="n">
         <v>99</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -2666,7 +2676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IQ3"/>
+  <dimension ref="A1:IR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2920,6 +2930,7 @@
     <col width="12" customWidth="1" min="249" max="249"/>
     <col width="12" customWidth="1" min="250" max="250"/>
     <col width="12" customWidth="1" min="251" max="251"/>
+    <col width="12" customWidth="1" min="252" max="252"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4178,6 +4189,11 @@
           <t>20260923</t>
         </is>
       </c>
+      <c r="IR1" s="1" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4877,6 +4893,9 @@
       <c r="IQ2" t="n">
         <v>104</v>
       </c>
+      <c r="IR2" t="n">
+        <v>102</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5635,6 +5654,9 @@
       </c>
       <c r="IQ3" t="n">
         <v>112</v>
+      </c>
+      <c r="IR3" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -5648,7 +5670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HX3"/>
+  <dimension ref="A1:HY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5883,6 +5905,7 @@
     <col width="12" customWidth="1" min="230" max="230"/>
     <col width="12" customWidth="1" min="231" max="231"/>
     <col width="12" customWidth="1" min="232" max="232"/>
+    <col width="12" customWidth="1" min="233" max="233"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7046,6 +7069,11 @@
           <t>20260923</t>
         </is>
       </c>
+      <c r="HY1" s="1" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7631,6 +7659,9 @@
       <c r="HX2" t="n">
         <v>39.63</v>
       </c>
+      <c r="HY2" t="n">
+        <v>50.05</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8332,6 +8363,9 @@
       </c>
       <c r="HX3" t="n">
         <v>32.49</v>
+      </c>
+      <c r="HY3" t="n">
+        <v>41.1</v>
       </c>
     </row>
   </sheetData>
@@ -8345,7 +8379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HC3"/>
+  <dimension ref="A1:HD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8559,6 +8593,7 @@
     <col width="12" customWidth="1" min="209" max="209"/>
     <col width="12" customWidth="1" min="210" max="210"/>
     <col width="12" customWidth="1" min="211" max="211"/>
+    <col width="12" customWidth="1" min="212" max="212"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9617,6 +9652,11 @@
           <t>20260923</t>
         </is>
       </c>
+      <c r="HD1" s="1" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10076,6 +10116,9 @@
       <c r="HC2" t="n">
         <v>6</v>
       </c>
+      <c r="HD2" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10714,6 +10757,9 @@
       </c>
       <c r="HC3" t="n">
         <v>16</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -10727,7 +10773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IG3"/>
+  <dimension ref="A1:IH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10971,6 +11017,7 @@
     <col width="10" customWidth="1" min="239" max="239"/>
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
+    <col width="10" customWidth="1" min="242" max="242"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11701,6 +11748,9 @@
       <c r="IG1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="IH1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12430,6 +12480,9 @@
       <c r="IG2" t="n">
         <v>133</v>
       </c>
+      <c r="IH2" t="n">
+        <v>73</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13158,6 +13211,9 @@
       </c>
       <c r="IG3" t="n">
         <v>123</v>
+      </c>
+      <c r="IH3" t="n">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -13171,7 +13227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU3"/>
+  <dimension ref="A1:EV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13325,6 +13381,7 @@
     <col width="10" customWidth="1" min="149" max="149"/>
     <col width="10" customWidth="1" min="150" max="150"/>
     <col width="10" customWidth="1" min="151" max="151"/>
+    <col width="10" customWidth="1" min="152" max="152"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13785,6 +13842,9 @@
       <c r="EU1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="EV1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14244,6 +14304,9 @@
       <c r="EU2" t="n">
         <v>99</v>
       </c>
+      <c r="EV2" t="n">
+        <v>92</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14702,6 +14765,9 @@
       </c>
       <c r="EU3" t="n">
         <v>83</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -14715,7 +14781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EU3"/>
+  <dimension ref="A1:EV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14869,6 +14935,7 @@
     <col width="10" customWidth="1" min="149" max="149"/>
     <col width="10" customWidth="1" min="150" max="150"/>
     <col width="10" customWidth="1" min="151" max="151"/>
+    <col width="10" customWidth="1" min="152" max="152"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15329,6 +15396,9 @@
       <c r="EU1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="EV1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15788,6 +15858,9 @@
       <c r="EU2" t="n">
         <v>62</v>
       </c>
+      <c r="EV2" t="n">
+        <v>47</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16246,6 +16319,9 @@
       </c>
       <c r="EU3" t="n">
         <v>51</v>
+      </c>
+      <c r="EV3" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -16259,7 +16335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HC3"/>
+  <dimension ref="A1:HD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16473,6 +16549,7 @@
     <col width="12" customWidth="1" min="209" max="209"/>
     <col width="12" customWidth="1" min="210" max="210"/>
     <col width="12" customWidth="1" min="211" max="211"/>
+    <col width="12" customWidth="1" min="212" max="212"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17531,6 +17608,11 @@
           <t>20260923</t>
         </is>
       </c>
+      <c r="HD1" s="1" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -17990,6 +18072,9 @@
       <c r="HC2" t="n">
         <v>105</v>
       </c>
+      <c r="HD2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18628,6 +18713,9 @@
       </c>
       <c r="HC3" t="n">
         <v>112</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -18641,7 +18729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IQ3"/>
+  <dimension ref="A1:IR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18895,6 +18983,7 @@
     <col width="12" customWidth="1" min="249" max="249"/>
     <col width="12" customWidth="1" min="250" max="250"/>
     <col width="12" customWidth="1" min="251" max="251"/>
+    <col width="12" customWidth="1" min="252" max="252"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20153,6 +20242,11 @@
           <t>20260923</t>
         </is>
       </c>
+      <c r="IR1" s="1" t="inlineStr">
+        <is>
+          <t>20260924</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20852,6 +20946,9 @@
       <c r="IQ2" t="n">
         <v>10.8</v>
       </c>
+      <c r="IR2" t="n">
+        <v>11.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21610,6 +21707,9 @@
       </c>
       <c r="IQ3" t="n">
         <v>3.17</v>
+      </c>
+      <c r="IR3" t="n">
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -21623,7 +21723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JJ3"/>
+  <dimension ref="A1:JK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21896,6 +21996,7 @@
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22713,6 +22814,9 @@
       <c r="JJ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="JK1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23526,6 +23630,9 @@
       <c r="JJ2" t="n">
         <v>747.6212</v>
       </c>
+      <c r="JK2" t="n">
+        <v>736.2781</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24341,6 +24448,9 @@
       </c>
       <c r="JJ3" t="n">
         <v>80.73999999999999</v>
+      </c>
+      <c r="JK3" t="n">
+        <v>77.05</v>
       </c>
     </row>
   </sheetData>
@@ -24354,7 +24464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JJ3"/>
+  <dimension ref="A1:JK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24627,6 +24737,7 @@
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25444,6 +25555,9 @@
       <c r="JJ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="JK1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26257,6 +26371,9 @@
       <c r="JJ2" t="n">
         <v>749.08</v>
       </c>
+      <c r="JK2" t="n">
+        <v>742.29</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27072,6 +27189,9 @@
       </c>
       <c r="JJ3" t="n">
         <v>81.2</v>
+      </c>
+      <c r="JK3" t="n">
+        <v>78.20999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -27085,7 +27205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JJ3"/>
+  <dimension ref="A1:JK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27358,6 +27478,7 @@
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28175,6 +28296,9 @@
       <c r="JJ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="JK1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -28988,6 +29112,9 @@
       <c r="JJ2" t="n">
         <v>744.688</v>
       </c>
+      <c r="JK2" t="n">
+        <v>731.67</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29803,6 +29930,9 @@
       </c>
       <c r="JJ3" t="n">
         <v>79.78</v>
+      </c>
+      <c r="JK3" t="n">
+        <v>75.61</v>
       </c>
     </row>
   </sheetData>
@@ -29816,7 +29946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JJ3"/>
+  <dimension ref="A1:JK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30089,6 +30219,7 @@
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30906,6 +31037,9 @@
       <c r="JJ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="JK1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31719,6 +31853,9 @@
       <c r="JJ2" t="n">
         <v>745.6993</v>
       </c>
+      <c r="JK2" t="n">
+        <v>734.25</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32534,6 +32671,9 @@
       </c>
       <c r="JJ3" t="n">
         <v>80.11</v>
+      </c>
+      <c r="JK3" t="n">
+        <v>76.4295</v>
       </c>
     </row>
   </sheetData>
@@ -32547,7 +32687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JJ3"/>
+  <dimension ref="A1:JK3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32820,6 +32960,7 @@
     <col width="12" customWidth="1" min="268" max="268"/>
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
+    <col width="12" customWidth="1" min="271" max="271"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33637,6 +33778,9 @@
       <c r="JJ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="JK1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34450,6 +34594,9 @@
       <c r="JJ2" t="n">
         <v>355336</v>
       </c>
+      <c r="JK2" t="n">
+        <v>969148</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35265,6 +35412,9 @@
       </c>
       <c r="JJ3" t="n">
         <v>1789031</v>
+      </c>
+      <c r="JK3" t="n">
+        <v>2722522</v>
       </c>
     </row>
   </sheetData>
@@ -35278,7 +35428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IQ3"/>
+  <dimension ref="A1:IR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35532,6 +35682,7 @@
     <col width="10" customWidth="1" min="249" max="249"/>
     <col width="10" customWidth="1" min="250" max="250"/>
     <col width="10" customWidth="1" min="251" max="251"/>
+    <col width="10" customWidth="1" min="252" max="252"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36292,6 +36443,9 @@
       <c r="IQ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="IR1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37051,6 +37205,9 @@
       <c r="IQ2" t="n">
         <v>100</v>
       </c>
+      <c r="IR2" t="n">
+        <v>70</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37809,6 +37966,9 @@
       </c>
       <c r="IQ3" t="n">
         <v>100</v>
+      </c>
+      <c r="IR3" t="n">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -37822,7 +37982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HC3"/>
+  <dimension ref="A1:HD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38036,6 +38196,7 @@
     <col width="10" customWidth="1" min="209" max="209"/>
     <col width="10" customWidth="1" min="210" max="210"/>
     <col width="10" customWidth="1" min="211" max="211"/>
+    <col width="10" customWidth="1" min="212" max="212"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38676,6 +38837,9 @@
       <c r="HC1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="HD1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39315,6 +39479,9 @@
       <c r="HC2" t="n">
         <v>100</v>
       </c>
+      <c r="HD2" t="n">
+        <v>85</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -39953,6 +40120,9 @@
       </c>
       <c r="HC3" t="n">
         <v>100</v>
+      </c>
+      <c r="HD3" t="n">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -39966,7 +40136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IQ3"/>
+  <dimension ref="A1:IR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40220,6 +40390,7 @@
     <col width="10" customWidth="1" min="249" max="249"/>
     <col width="10" customWidth="1" min="250" max="250"/>
     <col width="10" customWidth="1" min="251" max="251"/>
+    <col width="10" customWidth="1" min="252" max="252"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -40980,6 +41151,9 @@
       <c r="IQ1" s="1" t="n">
         <v>20260923</v>
       </c>
+      <c r="IR1" s="1" t="n">
+        <v>20260924</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41739,6 +41913,9 @@
       <c r="IQ2" t="n">
         <v>130</v>
       </c>
+      <c r="IR2" t="n">
+        <v>69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42497,6 +42674,9 @@
       </c>
       <c r="IQ3" t="n">
         <v>129</v>
+      </c>
+      <c r="IR3" t="n">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/US_Stocks_ETF.xlsx
+++ b/US_Stocks_ETF.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD3"/>
+  <dimension ref="A1:HE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -737,6 +737,7 @@
     <col width="10" customWidth="1" min="210" max="210"/>
     <col width="10" customWidth="1" min="211" max="211"/>
     <col width="10" customWidth="1" min="212" max="212"/>
+    <col width="10" customWidth="1" min="213" max="213"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1380,6 +1381,9 @@
       <c r="HD1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="HE1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2022,6 +2026,9 @@
       <c r="HD2" t="n">
         <v>71</v>
       </c>
+      <c r="HE2" t="n">
+        <v>101</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2663,6 +2670,9 @@
       </c>
       <c r="HD3" t="n">
         <v>56</v>
+      </c>
+      <c r="HE3" t="n">
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2676,7 +2686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IR3"/>
+  <dimension ref="A1:IS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2931,6 +2941,7 @@
     <col width="12" customWidth="1" min="250" max="250"/>
     <col width="12" customWidth="1" min="251" max="251"/>
     <col width="12" customWidth="1" min="252" max="252"/>
+    <col width="12" customWidth="1" min="253" max="253"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4194,6 +4205,11 @@
           <t>20260924</t>
         </is>
       </c>
+      <c r="IS1" s="1" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4896,6 +4912,9 @@
       <c r="IR2" t="n">
         <v>102</v>
       </c>
+      <c r="IS2" t="n">
+        <v>103</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5657,6 +5676,9 @@
       </c>
       <c r="IR3" t="n">
         <v>106</v>
+      </c>
+      <c r="IS3" t="n">
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -5670,7 +5692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HY3"/>
+  <dimension ref="A1:HZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5906,6 +5928,7 @@
     <col width="12" customWidth="1" min="231" max="231"/>
     <col width="12" customWidth="1" min="232" max="232"/>
     <col width="12" customWidth="1" min="233" max="233"/>
+    <col width="12" customWidth="1" min="234" max="234"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7074,6 +7097,11 @@
           <t>20260924</t>
         </is>
       </c>
+      <c r="HZ1" s="1" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7662,6 +7690,9 @@
       <c r="HY2" t="n">
         <v>50.05</v>
       </c>
+      <c r="HZ2" t="n">
+        <v>66.20999999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -8366,6 +8397,9 @@
       </c>
       <c r="HY3" t="n">
         <v>41.1</v>
+      </c>
+      <c r="HZ3" t="n">
+        <v>55.85</v>
       </c>
     </row>
   </sheetData>
@@ -8379,7 +8413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD3"/>
+  <dimension ref="A1:HE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8594,6 +8628,7 @@
     <col width="12" customWidth="1" min="210" max="210"/>
     <col width="12" customWidth="1" min="211" max="211"/>
     <col width="12" customWidth="1" min="212" max="212"/>
+    <col width="12" customWidth="1" min="213" max="213"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9657,6 +9692,11 @@
           <t>20260924</t>
         </is>
       </c>
+      <c r="HE1" s="1" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10119,6 +10159,9 @@
       <c r="HD2" t="n">
         <v>16</v>
       </c>
+      <c r="HE2" t="n">
+        <v>9</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10759,6 +10802,9 @@
         <v>16</v>
       </c>
       <c r="HD3" t="n">
+        <v>25</v>
+      </c>
+      <c r="HE3" t="n">
         <v>25</v>
       </c>
     </row>
@@ -10773,7 +10819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IH3"/>
+  <dimension ref="A1:II3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11018,6 +11064,7 @@
     <col width="10" customWidth="1" min="240" max="240"/>
     <col width="10" customWidth="1" min="241" max="241"/>
     <col width="10" customWidth="1" min="242" max="242"/>
+    <col width="10" customWidth="1" min="243" max="243"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11751,6 +11798,9 @@
       <c r="IH1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="II1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -12483,6 +12533,9 @@
       <c r="IH2" t="n">
         <v>73</v>
       </c>
+      <c r="II2" t="n">
+        <v>107</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13214,6 +13267,9 @@
       </c>
       <c r="IH3" t="n">
         <v>62</v>
+      </c>
+      <c r="II3" t="n">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -13227,7 +13283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EV3"/>
+  <dimension ref="A1:EW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -13382,6 +13438,7 @@
     <col width="10" customWidth="1" min="150" max="150"/>
     <col width="10" customWidth="1" min="151" max="151"/>
     <col width="10" customWidth="1" min="152" max="152"/>
+    <col width="10" customWidth="1" min="153" max="153"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13845,6 +13902,9 @@
       <c r="EV1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="EW1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14307,6 +14367,9 @@
       <c r="EV2" t="n">
         <v>92</v>
       </c>
+      <c r="EW2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14768,6 +14831,9 @@
       </c>
       <c r="EV3" t="n">
         <v>74</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -14781,7 +14847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EV3"/>
+  <dimension ref="A1:EW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14936,6 +15002,7 @@
     <col width="10" customWidth="1" min="150" max="150"/>
     <col width="10" customWidth="1" min="151" max="151"/>
     <col width="10" customWidth="1" min="152" max="152"/>
+    <col width="10" customWidth="1" min="153" max="153"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -15399,6 +15466,9 @@
       <c r="EV1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="EW1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -15861,6 +15931,9 @@
       <c r="EV2" t="n">
         <v>47</v>
       </c>
+      <c r="EW2" t="n">
+        <v>62</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16322,6 +16395,9 @@
       </c>
       <c r="EV3" t="n">
         <v>31</v>
+      </c>
+      <c r="EW3" t="n">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -16335,7 +16411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD3"/>
+  <dimension ref="A1:HE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -16550,6 +16626,7 @@
     <col width="12" customWidth="1" min="210" max="210"/>
     <col width="12" customWidth="1" min="211" max="211"/>
     <col width="12" customWidth="1" min="212" max="212"/>
+    <col width="12" customWidth="1" min="213" max="213"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -17613,6 +17690,11 @@
           <t>20260924</t>
         </is>
       </c>
+      <c r="HE1" s="1" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -18075,6 +18157,9 @@
       <c r="HD2" t="n">
         <v>103</v>
       </c>
+      <c r="HE2" t="n">
+        <v>104</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -18716,6 +18801,9 @@
       </c>
       <c r="HD3" t="n">
         <v>106</v>
+      </c>
+      <c r="HE3" t="n">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -18729,7 +18817,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IR3"/>
+  <dimension ref="A1:IS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -18984,6 +19072,7 @@
     <col width="12" customWidth="1" min="250" max="250"/>
     <col width="12" customWidth="1" min="251" max="251"/>
     <col width="12" customWidth="1" min="252" max="252"/>
+    <col width="12" customWidth="1" min="253" max="253"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20247,6 +20336,11 @@
           <t>20260924</t>
         </is>
       </c>
+      <c r="IS1" s="1" t="inlineStr">
+        <is>
+          <t>20260925</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -20949,6 +21043,9 @@
       <c r="IR2" t="n">
         <v>11.29</v>
       </c>
+      <c r="IS2" t="n">
+        <v>12.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -21710,6 +21807,9 @@
       </c>
       <c r="IR3" t="n">
         <v>3.3</v>
+      </c>
+      <c r="IS3" t="n">
+        <v>3.68</v>
       </c>
     </row>
   </sheetData>
@@ -21723,7 +21823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JK3"/>
+  <dimension ref="A1:JL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21997,6 +22097,7 @@
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
     <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -22817,6 +22918,9 @@
       <c r="JK1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="JL1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23633,6 +23737,9 @@
       <c r="JK2" t="n">
         <v>736.2781</v>
       </c>
+      <c r="JL2" t="n">
+        <v>744</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24451,6 +24558,9 @@
       </c>
       <c r="JK3" t="n">
         <v>77.05</v>
+      </c>
+      <c r="JL3" t="n">
+        <v>79.47</v>
       </c>
     </row>
   </sheetData>
@@ -24464,7 +24574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JK3"/>
+  <dimension ref="A1:JL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -24738,6 +24848,7 @@
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
     <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -25558,6 +25669,9 @@
       <c r="JK1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="JL1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -26374,6 +26488,9 @@
       <c r="JK2" t="n">
         <v>742.29</v>
       </c>
+      <c r="JL2" t="n">
+        <v>747.0599999999999</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -27192,6 +27309,9 @@
       </c>
       <c r="JK3" t="n">
         <v>78.20999999999999</v>
+      </c>
+      <c r="JL3" t="n">
+        <v>80.43000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -27205,7 +27325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JK3"/>
+  <dimension ref="A1:JL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -27479,6 +27599,7 @@
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
     <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28299,6 +28420,9 @@
       <c r="JK1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="JL1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29115,6 +29239,9 @@
       <c r="JK2" t="n">
         <v>731.67</v>
       </c>
+      <c r="JL2" t="n">
+        <v>737.105</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -29933,6 +30060,9 @@
       </c>
       <c r="JK3" t="n">
         <v>75.61</v>
+      </c>
+      <c r="JL3" t="n">
+        <v>78.58</v>
       </c>
     </row>
   </sheetData>
@@ -29946,7 +30076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JK3"/>
+  <dimension ref="A1:JL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -30220,6 +30350,7 @@
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
     <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31040,6 +31171,9 @@
       <c r="JK1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="JL1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -31856,6 +31990,9 @@
       <c r="JK2" t="n">
         <v>734.25</v>
       </c>
+      <c r="JL2" t="n">
+        <v>744.24</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -32674,6 +32811,9 @@
       </c>
       <c r="JK3" t="n">
         <v>76.4295</v>
+      </c>
+      <c r="JL3" t="n">
+        <v>79.52</v>
       </c>
     </row>
   </sheetData>
@@ -32687,7 +32827,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:JK3"/>
+  <dimension ref="A1:JL3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -32961,6 +33101,7 @@
     <col width="12" customWidth="1" min="269" max="269"/>
     <col width="12" customWidth="1" min="270" max="270"/>
     <col width="12" customWidth="1" min="271" max="271"/>
+    <col width="12" customWidth="1" min="272" max="272"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -33781,6 +33922,9 @@
       <c r="JK1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="JL1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -34597,6 +34741,9 @@
       <c r="JK2" t="n">
         <v>969148</v>
       </c>
+      <c r="JL2" t="n">
+        <v>423757</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -35415,6 +35562,9 @@
       </c>
       <c r="JK3" t="n">
         <v>2722522</v>
+      </c>
+      <c r="JL3" t="n">
+        <v>2211286</v>
       </c>
     </row>
   </sheetData>
@@ -35428,7 +35578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IR3"/>
+  <dimension ref="A1:IS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -35683,6 +35833,7 @@
     <col width="10" customWidth="1" min="250" max="250"/>
     <col width="10" customWidth="1" min="251" max="251"/>
     <col width="10" customWidth="1" min="252" max="252"/>
+    <col width="10" customWidth="1" min="253" max="253"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -36446,6 +36597,9 @@
       <c r="IR1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="IS1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -37208,6 +37362,9 @@
       <c r="IR2" t="n">
         <v>70</v>
       </c>
+      <c r="IS2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -37969,6 +38126,9 @@
       </c>
       <c r="IR3" t="n">
         <v>68</v>
+      </c>
+      <c r="IS3" t="n">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -37982,7 +38142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HD3"/>
+  <dimension ref="A1:HE3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -38197,6 +38357,7 @@
     <col width="10" customWidth="1" min="210" max="210"/>
     <col width="10" customWidth="1" min="211" max="211"/>
     <col width="10" customWidth="1" min="212" max="212"/>
+    <col width="10" customWidth="1" min="213" max="213"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -38840,6 +39001,9 @@
       <c r="HD1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="HE1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -39482,6 +39646,9 @@
       <c r="HD2" t="n">
         <v>85</v>
       </c>
+      <c r="HE2" t="n">
+        <v>98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40123,6 +40290,9 @@
       </c>
       <c r="HD3" t="n">
         <v>83</v>
+      </c>
+      <c r="HE3" t="n">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -40136,7 +40306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:IR3"/>
+  <dimension ref="A1:IS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -40391,6 +40561,7 @@
     <col width="10" customWidth="1" min="250" max="250"/>
     <col width="10" customWidth="1" min="251" max="251"/>
     <col width="10" customWidth="1" min="252" max="252"/>
+    <col width="10" customWidth="1" min="253" max="253"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -41154,6 +41325,9 @@
       <c r="IR1" s="1" t="n">
         <v>20260924</v>
       </c>
+      <c r="IS1" s="1" t="n">
+        <v>20260925</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -41916,6 +42090,9 @@
       <c r="IR2" t="n">
         <v>69</v>
       </c>
+      <c r="IS2" t="n">
+        <v>96</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -42677,6 +42854,9 @@
       </c>
       <c r="IR3" t="n">
         <v>65</v>
+      </c>
+      <c r="IS3" t="n">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
